--- a/output/contract_anchor_db/Hand主播档案仍未命中_替换后_20260629.xlsx
+++ b/output/contract_anchor_db/Hand主播档案仍未命中_替换后_20260629.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="188条清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="187条清单" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'188条清单'!$A$1:$R$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'187条清单'!$A$1:$R$188</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8">
@@ -627,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R189"/>
+  <dimension ref="A1:R188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -760,17 +760,17 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>CQ-J-202311001</t>
+          <t>HH-B-202205004</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>舱全-巨龙-斗鱼-小伞四方联合运营合同</t>
+          <t>斗鱼直播一部游戏组-骆歆（骆雨婷）-独家经纪约</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>2027-08-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
@@ -780,39 +780,39 @@
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>27129</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>27129</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr"/>
       <c r="K2" s="9" t="inlineStr"/>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>金佳冬</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N2" s="8" t="inlineStr">
         <is>
-          <t>金佳冬</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="O2" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P2" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="Q2" s="8" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="R2" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202205004</t>
+          <t>HH-B-202205004-S1</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>斗鱼直播一部游戏组-骆歆（骆雨婷）-独家经纪约</t>
+          <t>合同主体变更四方协议-厚翰骆雨婷卓晨快权</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>法务确认</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
@@ -928,59 +928,59 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202205004-S1</t>
+          <t>HH-B-202210007</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>合同主体变更四方协议-厚翰骆雨婷卓晨快权</t>
+          <t>头部经纪组主播赵松琪（松琪酱）独家经纪合同</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>法务确认</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="9" t="inlineStr"/>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>梁家斌</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>梁家斌</t>
         </is>
       </c>
       <c r="O4" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q4" s="8" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="R4" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202210007</t>
+          <t>HH-B-202302002</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>头部经纪组主播赵松琪（松琪酱）独家经纪合同</t>
+          <t>斗鱼主播flower（李明浩）独家经济合同</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -1032,19 +1032,19 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>24074</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>24074</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr"/>
       <c r="K5" s="11" t="inlineStr"/>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>梁家斌</t>
+          <t>徐涛</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>梁家斌</t>
+          <t>徐涛</t>
         </is>
       </c>
       <c r="O5" s="10" t="inlineStr">
@@ -1096,59 +1096,59 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202302002</t>
+          <t>HH-B-202303004</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>斗鱼主播flower（李明浩）独家经济合同</t>
+          <t>三木老师独家经纪合同_20220506_V2.2</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2028-04-01</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>法务确认</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>24074</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>24074</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="9" t="inlineStr"/>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>徐涛</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>徐涛</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="O6" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P6" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="Q6" s="8" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="R6" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -1180,32 +1180,32 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202303004</t>
+          <t>HH-B-202306004</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>三木老师独家经纪合同_20220506_V2.2</t>
+          <t>斗鱼英雄联盟主播-熊猫大G经纪约</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>2028-04-01</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>法务确认</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>24938</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>24938</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr"/>
@@ -1264,17 +1264,17 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202306004</t>
+          <t>HH-B-202308005</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>斗鱼英雄联盟主播-熊猫大G经纪约</t>
+          <t>斗鱼主播王波波卡特ovo-运营二组-经纪约</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>2027-03-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1284,19 +1284,19 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>26645</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>26645</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr"/>
       <c r="K8" s="9" t="inlineStr"/>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="O8" s="8" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="P8" s="8" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="Q8" s="8" t="inlineStr">
@@ -1348,59 +1348,59 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202308005</t>
+          <t>HH-B-202310012</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>斗鱼主播王波波卡特ovo-运营二组-经纪约</t>
+          <t>头部经纪组主播刘鎏（六六）独家经纪合同</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>26645</t>
+          <t>27012</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>26645</t>
+          <t>27012</t>
         </is>
       </c>
       <c r="J9" s="10" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>梁家斌</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>梁家斌</t>
         </is>
       </c>
       <c r="O9" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q9" s="10" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -1432,59 +1432,59 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202310012</t>
+          <t>HH-B-202402001</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>头部经纪组主播刘鎏（六六）独家经纪合同</t>
+          <t>刘焱独家经纪约</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>27012</t>
+          <t>28121</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>27012</t>
+          <t>28121</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr"/>
       <c r="K10" s="9" t="inlineStr"/>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>梁家斌</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>梁家斌</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="O10" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P10" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="Q10" s="8" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="R10" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202402001</t>
+          <t>HH-B-202402002</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>刘焱独家经纪约</t>
+          <t>何皓独家经纪约</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>28121</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>28121</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr"/>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202402002</t>
+          <t>HH-B-202402003</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>何皓独家经纪约</t>
+          <t>胡齐萌独家经纪约</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>28122</t>
+          <t>28123</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>28122</t>
+          <t>28123</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr"/>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202402003</t>
+          <t>HH-B-202402004</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>胡齐萌独家经纪约</t>
+          <t>张狄深独家经纪约</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -1699,17 +1699,17 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>28123</t>
+          <t>28126</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>28123</t>
+          <t>28126</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr"/>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202402004</t>
+          <t>HH-B-202402005</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>张狄深独家经纪约</t>
+          <t>肖龙独家经纪约</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -1783,17 +1783,17 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>28126</t>
+          <t>28127</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>28126</t>
+          <t>28127</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr"/>
@@ -1852,39 +1852,39 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202402005</t>
+          <t>HH-B-202405004</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>肖龙独家经纪约</t>
+          <t>厚翰小吖独家直播合作协议</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>28127</t>
+          <t>28699</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>28127</t>
+          <t>28699</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr"/>
       <c r="K15" s="11" t="inlineStr"/>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>何宇</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>何宇</t>
         </is>
       </c>
       <c r="O15" s="10" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="P15" s="10" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>何宇</t>
         </is>
       </c>
       <c r="Q15" s="10" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202405004</t>
+          <t>HH-B-202405004-S1</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>厚翰小吖独家直播合作协议</t>
+          <t>厚翰小吖独家直播协议之解除协议</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202405004-S1</t>
+          <t>HH-B-202405005</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>厚翰小吖独家直播协议之解除协议</t>
+          <t>厚翰秦虹独家直播合作协议</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
@@ -2040,12 +2040,12 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>28699</t>
+          <t>28686</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>28699</t>
+          <t>28686</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr"/>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202405005</t>
+          <t>HH-B-202405005-S1</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>厚翰秦虹独家直播合作协议</t>
+          <t>厚翰秦虹独家直播协议之解除协议</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -2188,17 +2188,17 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202405005-S1</t>
+          <t>HH-B-202406004</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>厚翰秦虹独家直播协议之解除协议</t>
+          <t>独家经纪约 唐唐</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -2208,19 +2208,19 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>28686</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>28686</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr"/>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>何宇</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>何宇</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="O19" s="10" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>何宇</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
@@ -2272,17 +2272,17 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202406004</t>
+          <t>HH-B-202406008</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>独家经纪约 唐唐</t>
+          <t>快手直播运营管理部-DNF大嘴（孔令杰）-独家合作协议</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
@@ -2292,19 +2292,19 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>28741</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>28741</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr"/>
       <c r="K20" s="9" t="inlineStr"/>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="O20" s="8" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="P20" s="8" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="Q20" s="8" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202406008</t>
+          <t>HH-B-202406008-S1</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>快手直播运营管理部-DNF大嘴（孔令杰）-独家合作协议</t>
+          <t>快手直播运营管理部-DNF大嘴（孔令杰）-独家合作协议之补充协议</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202406008-S1</t>
+          <t>HH-B-202406009</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>快手直播运营管理部-DNF大嘴（孔令杰）-独家合作协议之补充协议</t>
+          <t>经纪约-龚凌凤-B站主播</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2027-06-19</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
@@ -2460,19 +2460,19 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>28741</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>28741</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr"/>
       <c r="K22" s="9" t="inlineStr"/>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="O22" s="8" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P22" s="8" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="Q22" s="8" t="inlineStr">
@@ -2524,17 +2524,17 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202406009</t>
+          <t>HH-B-202409002</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>经纪约-龚凌凤-B站主播</t>
+          <t>快手直播运营管理部-袁中直（屿秋）-独家合作协议</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>2027-06-19</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -2544,19 +2544,19 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>29151</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>29151</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr"/>
       <c r="K23" s="11" t="inlineStr"/>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="O23" s="10" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="P23" s="10" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="Q23" s="10" t="inlineStr">
@@ -2608,17 +2608,17 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202409002</t>
+          <t>HH-B-202409005</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>快手直播运营管理部-袁中直（屿秋）-独家合作协议</t>
+          <t>陈世豪（小七seven）独家经纪合同</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -2628,19 +2628,19 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>29151</t>
+          <t>14986</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>29151</t>
+          <t>14986</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr"/>
       <c r="K24" s="9" t="inlineStr"/>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="O24" s="8" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="P24" s="8" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="Q24" s="8" t="inlineStr">
@@ -2692,39 +2692,39 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202409005</t>
+          <t>HH-B-202411001</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>陈世豪（小七seven）独家经纪合同</t>
+          <t>厚翰-解说潇洒独家经纪约</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>14986</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>14986</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr"/>
       <c r="K25" s="11" t="inlineStr"/>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>王洛迪</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>王洛迪</t>
         </is>
       </c>
       <c r="O25" s="10" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="P25" s="10" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>王洛迪</t>
         </is>
       </c>
       <c r="Q25" s="10" t="inlineStr">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202411001</t>
+          <t>HH-B-202411002</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>厚翰-解说潇洒独家经纪约</t>
+          <t>厚翰-解说老王独家经纪约</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -2796,39 +2796,39 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>21865</t>
+          <t>21870</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>21865</t>
+          <t>21870</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>王洛迪</t>
+          <t>金佳冬</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>王洛迪</t>
+          <t>金佳冬</t>
         </is>
       </c>
       <c r="O26" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P26" s="8" t="inlineStr">
         <is>
-          <t>王洛迪</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q26" s="8" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="R26" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -2860,59 +2860,59 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202411002</t>
+          <t>HH-B-202505001</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>厚翰-解说老王独家经纪约</t>
+          <t>赵玲琳（圈圈）独家经纪合同</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-04-30</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>21870</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>21870</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr"/>
       <c r="K27" s="11" t="inlineStr"/>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>金佳冬</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
-          <t>金佳冬</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="O27" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="Q27" s="10" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202505001</t>
+          <t>HH-B-202507001</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>赵玲琳（圈圈）独家经纪合同</t>
+          <t>【厚翰审核】厚翰-若风&amp;风曦-独家合作协议</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>2027-04-30</t>
+          <t>2028-07-14</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -2964,39 +2964,39 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>30192</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>30192</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr"/>
       <c r="K28" s="9" t="inlineStr"/>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>陈金霞</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>陈金霞</t>
         </is>
       </c>
       <c r="O28" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P28" s="8" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q28" s="8" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="R28" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>HH-B-202507001</t>
+          <t>HH-B-202507001-S1</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>【厚翰审核】厚翰-若风&amp;风曦-独家合作协议</t>
+          <t>【厚翰审核】厚翰-若风-房屋抵押合同</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
@@ -3112,17 +3112,17 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>HH-B-202507001-S1</t>
+          <t>HH-O-202307001</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>【厚翰审核】厚翰-若风-房屋抵押合同</t>
+          <t>主播转会协议-伍艾怡</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>2028-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
@@ -3130,21 +3130,13 @@
           <t>归档</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>30192</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>30192</t>
-        </is>
-      </c>
+      <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr"/>
       <c r="J30" s="8" t="inlineStr"/>
       <c r="K30" s="9" t="inlineStr"/>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>陈金霞</t>
+          <t>徐恒</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
@@ -3154,7 +3146,7 @@
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>陈金霞</t>
+          <t>徐恒</t>
         </is>
       </c>
       <c r="O30" s="8" t="inlineStr">
@@ -3196,17 +3188,17 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>HH-O-202307001</t>
+          <t>HH-O-202410001</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>主播转会协议-伍艾怡</t>
+          <t>厚翰-B站-主播转会协议-我方买入-游戏主播-刘剑华（库库_sama）</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2027-10-31</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -3220,7 +3212,7 @@
       <c r="K31" s="11" t="inlineStr"/>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>徐恒</t>
+          <t>王梅</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr">
@@ -3230,7 +3222,7 @@
       </c>
       <c r="N31" s="10" t="inlineStr">
         <is>
-          <t>徐恒</t>
+          <t>姚继骏</t>
         </is>
       </c>
       <c r="O31" s="10" t="inlineStr">
@@ -3272,17 +3264,17 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>HH-O-202410001</t>
+          <t>HH-O-202507001</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>厚翰-B站-主播转会协议-我方买入-游戏主播-刘剑华（库库_sama）</t>
+          <t>主播合作协议</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>2027-10-31</t>
+          <t>2028-05-31</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -3296,27 +3288,27 @@
       <c r="K32" s="9" t="inlineStr"/>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>王梅</t>
+          <t>葛垚</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>姚继骏</t>
+          <t>葛垚</t>
         </is>
       </c>
       <c r="O32" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P32" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>葛垚</t>
         </is>
       </c>
       <c r="Q32" s="8" t="inlineStr">
@@ -3326,7 +3318,7 @@
       </c>
       <c r="R32" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -3348,17 +3340,17 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>HH-O-202507001</t>
+          <t>HH-O-202602001</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>主播合作协议</t>
+          <t>赵礼杰独家合作协议</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>2028-05-31</t>
+          <t>2027-09-01</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -3372,7 +3364,7 @@
       <c r="K33" s="11" t="inlineStr"/>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>葛垚</t>
+          <t>张卓睿</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
@@ -3382,7 +3374,7 @@
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
-          <t>葛垚</t>
+          <t>张卓睿</t>
         </is>
       </c>
       <c r="O33" s="10" t="inlineStr">
@@ -3392,7 +3384,7 @@
       </c>
       <c r="P33" s="10" t="inlineStr">
         <is>
-          <t>葛垚</t>
+          <t>张卓睿</t>
         </is>
       </c>
       <c r="Q33" s="10" t="inlineStr">
@@ -3424,17 +3416,17 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>HH-O-202602001</t>
+          <t>HH-O-202605001</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>赵礼杰独家合作协议</t>
+          <t>体坛-厚翰 EWC 格斗项目合作协议</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>2027-09-01</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -3448,27 +3440,27 @@
       <c r="K34" s="9" t="inlineStr"/>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>张卓睿</t>
+          <t>李文敬</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>张卓睿</t>
+          <t>李文敬</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P34" s="8" t="inlineStr">
         <is>
-          <t>张卓睿</t>
+          <t>汤澄</t>
         </is>
       </c>
       <c r="Q34" s="8" t="inlineStr">
@@ -3478,7 +3470,7 @@
       </c>
       <c r="R34" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪; 法务CSV合同流程接收人最终覆盖为汤澄</t>
         </is>
       </c>
     </row>
@@ -3500,51 +3492,59 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>HH-O-202605001</t>
+          <t>HH-P-202404001</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>体坛-厚翰 EWC 格斗项目合作协议</t>
+          <t>小森未央斗鱼官签三方约</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr"/>
-      <c r="I35" s="10" t="inlineStr"/>
+          <t>上传电子档</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>28343</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>28343</t>
+        </is>
+      </c>
       <c r="J35" s="10" t="inlineStr"/>
       <c r="K35" s="11" t="inlineStr"/>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>李文敬</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N35" s="10" t="inlineStr">
         <is>
-          <t>李文敬</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="O35" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr">
         <is>
-          <t>汤澄</t>
+          <t>张兆庆</t>
         </is>
       </c>
       <c r="Q35" s="10" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="R35" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪; 法务CSV合同流程接收人最终覆盖为汤澄</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -3576,17 +3576,17 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>HH-P-202404001</t>
+          <t>HH-P-202504002</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>小森未央斗鱼官签三方约</t>
+          <t>FML直播一部游戏组-林炜翔-《虎牙直播合作协议》</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>2027-03-31</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -3596,19 +3596,19 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>28343</t>
+          <t>24461</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>28343</t>
+          <t>24461</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr"/>
       <c r="K36" s="9" t="inlineStr"/>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="O36" s="8" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P36" s="8" t="inlineStr">
         <is>
-          <t>张兆庆</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="Q36" s="8" t="inlineStr">
@@ -3660,59 +3660,59 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>HH-P-202504002</t>
+          <t>JZ-B-202402002</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>FML直播一部游戏组-林炜翔-《虎牙直播合作协议》</t>
+          <t>抖音团播-蓝少杰-独家合作合同</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>上传电子档</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>24461</t>
+          <t>28129</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>24461</t>
+          <t>28129</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr"/>
       <c r="K37" s="11" t="inlineStr"/>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>周鑫</t>
         </is>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N37" s="10" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>周鑫</t>
         </is>
       </c>
       <c r="O37" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P37" s="10" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q37" s="10" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="R37" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -3744,17 +3744,17 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>JZ-B-202402002</t>
+          <t>JZ-B-202403001-S1</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>抖音团播-蓝少杰-独家合作合同</t>
+          <t>金蕊-补充协议</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>28129</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>28129</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr"/>
@@ -3828,12 +3828,12 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>JZ-B-202403001-S1</t>
+          <t>JZ-B-202403001-S1-N</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>金蕊-补充协议</t>
+          <t>交友-金蕊-解除协议</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
@@ -3912,17 +3912,17 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>JZ-B-202403001-S1-N</t>
+          <t>JZ-B-202403008</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>交友-金蕊-解除协议</t>
+          <t>抖音团播-项淑婷-独家合作合同</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr"/>
@@ -3996,17 +3996,17 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>JZ-B-202403008</t>
+          <t>JZ-B-202404002</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>抖音团播-项淑婷-独家合作合同</t>
+          <t>抖音团播-甘永鑫-独家合作合同</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>28291</t>
+          <t>28289</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>28291</t>
+          <t>28289</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr"/>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>JZ-B-202404002</t>
+          <t>JZ-B-202404003</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>抖音团播-甘永鑫-独家合作合同</t>
+          <t>抖音团播-张维明-独家合作合同</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>28289</t>
+          <t>28288</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>28289</t>
+          <t>28288</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr"/>
@@ -4164,17 +4164,17 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>JZ-B-202404003</t>
+          <t>JZ-B-202404004</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>抖音团播-张维明-独家合作合同</t>
+          <t>抖音团播-刘雨-独家合作合同</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>28288</t>
+          <t>28290</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>28288</t>
+          <t>28290</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr"/>
@@ -4248,17 +4248,17 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>JZ-B-202404004</t>
+          <t>JZ-B-202404007</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>抖音团播-刘雨-独家合作合同</t>
+          <t>抖音团播-马永旺-独家合作合同</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr"/>
@@ -4332,17 +4332,17 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>JZ-B-202404007</t>
+          <t>JZ-B-202405001</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>抖音团播-马永旺-独家合作合同</t>
+          <t>抖音团播-吴仕军-独家合作合同</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>28566</t>
+          <t>28581</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>28566</t>
+          <t>28581</t>
         </is>
       </c>
       <c r="J45" s="10" t="inlineStr"/>
@@ -4416,17 +4416,17 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>JZ-B-202405001</t>
+          <t>JZ-B-202405002</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>抖音团播-吴仕军-独家合作合同</t>
+          <t>抖音团播-陈俊霖-独家合作合同</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>28587</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>28587</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr"/>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>JZ-B-202405002</t>
+          <t>JZ-B-202405003</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>抖音团播-陈俊霖-独家合作合同</t>
+          <t>抖音团播-张惠萍-独家合作合同</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>28587</t>
+          <t>28588</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>28587</t>
+          <t>28588</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr"/>
@@ -4584,17 +4584,17 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>JZ-B-202405003</t>
+          <t>JZ-B-202410001</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>抖音团播-张惠萍-独家合作合同</t>
+          <t>抖音团播-黄可涵-独家合作合同</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>28588</t>
+          <t>29292</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>28588</t>
+          <t>29292</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr"/>
@@ -4668,17 +4668,17 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>JZ-B-202410001</t>
+          <t>JZ-B-202410002</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>抖音团播-黄可涵-独家合作合同</t>
+          <t>抖音团播-郑婌婷-独家合作合同</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>29292</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>29292</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr"/>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>JZ-B-202410002</t>
+          <t>JZ-B-202410003</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>抖音团播-郑婌婷-独家合作合同</t>
+          <t>抖音团播-朱镕镥-独家合作合同</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>29300</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>29300</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr"/>
@@ -4836,39 +4836,39 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>JZ-B-202410003</t>
+          <t>LJ-P-202305001</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>抖音团播-朱镕镥-独家合作合同</t>
+          <t>快手直播主播合作协议（刘冰洁、快手、乐竞）</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>上传电子档</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="J51" s="10" t="inlineStr"/>
       <c r="K51" s="11" t="inlineStr"/>
       <c r="L51" s="10" t="inlineStr">
         <is>
-          <t>周鑫</t>
+          <t>刘禹岐</t>
         </is>
       </c>
       <c r="M51" s="10" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="N51" s="10" t="inlineStr">
         <is>
-          <t>周鑫</t>
+          <t>刘禹岐</t>
         </is>
       </c>
       <c r="O51" s="10" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>LJ-P-202305001</t>
+          <t>LJ-P-202305003</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>快手直播主播合作协议（刘冰洁、快手、乐竞）</t>
+          <t>快手直播主播合作协议（谭雅婷、快手、乐竞）</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -4940,19 +4940,19 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>24692</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>24692</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr"/>
       <c r="K52" s="9" t="inlineStr"/>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>刘禹岐</t>
+          <t>邱成业</t>
         </is>
       </c>
       <c r="M52" s="8" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>刘禹岐</t>
+          <t>邱成业</t>
         </is>
       </c>
       <c r="O52" s="8" t="inlineStr">
@@ -5004,39 +5004,39 @@
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>LJ-P-202305003</t>
+          <t>LZ-B-202202211</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>快手直播主播合作协议（谭雅婷、快手、乐竞）</t>
+          <t>独家合作协议（抖音，李梦尹，李梦颖）</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>上传电子档</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="J53" s="10" t="inlineStr"/>
       <c r="K53" s="11" t="inlineStr"/>
       <c r="L53" s="10" t="inlineStr">
         <is>
-          <t>邱成业</t>
+          <t>尹雨晴</t>
         </is>
       </c>
       <c r="M53" s="10" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="N53" s="10" t="inlineStr">
         <is>
-          <t>邱成业</t>
+          <t>石磊</t>
         </is>
       </c>
       <c r="O53" s="10" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202202211</t>
+          <t>LZ-B-202202211-N</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>独家合作协议（抖音，李梦尹，李梦颖）</t>
+          <t>李梦尹-补充协议（三）</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -5120,12 +5120,12 @@
       <c r="K54" s="9" t="inlineStr"/>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>尹雨晴</t>
+          <t>雍欣</t>
         </is>
       </c>
       <c r="M54" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P54" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>雍欣</t>
         </is>
       </c>
       <c r="Q54" s="8" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="R54" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>李梦尹-补充协议（三）</t>
+          <t>抖音-李梦尹-和解协议</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
@@ -5204,7 +5204,7 @@
       <c r="K55" s="11" t="inlineStr"/>
       <c r="L55" s="10" t="inlineStr">
         <is>
-          <t>雍欣</t>
+          <t>罗元泽</t>
         </is>
       </c>
       <c r="M55" s="10" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P55" s="10" t="inlineStr">
         <is>
-          <t>雍欣</t>
+          <t>罗元泽</t>
         </is>
       </c>
       <c r="Q55" s="10" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202202211-N</t>
+          <t>LZ-B-202202211-S2</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>抖音-李梦尹-和解协议</t>
+          <t>补充协议-【抖音-成都尹乐家-李梦颖】</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -5288,12 +5288,12 @@
       <c r="K56" s="9" t="inlineStr"/>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>罗元泽</t>
+          <t>李敬</t>
         </is>
       </c>
       <c r="M56" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="P56" s="8" t="inlineStr">
         <is>
-          <t>罗元泽</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q56" s="8" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="R56" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202202211-S2</t>
+          <t>LZ-B-202202211-S3</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
@@ -5424,32 +5424,32 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202202211-S3</t>
+          <t>LZ-B-202212004</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>补充协议-【抖音-成都尹乐家-李梦颖】</t>
+          <t>独家经纪约—何光建（抖音、何滴儿）</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>2027-07-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>法务确认</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>16336</t>
+          <t>23784</t>
         </is>
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>16336</t>
+          <t>23784</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr"/>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>石磊</t>
+          <t>李敬</t>
         </is>
       </c>
       <c r="O58" s="8" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202212004</t>
+          <t>LZ-B-202212004-S1</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>独家经纪约—何光建（抖音、何滴儿）</t>
+          <t>补充协议-抖音，何光建</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>法务确认</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202212004-S1</t>
+          <t>LZ-B-202212004-S2</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>补充协议-抖音，何光建</t>
+          <t>抖音-何光建执行和解协议</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -5624,19 +5624,19 @@
       <c r="K60" s="9" t="inlineStr"/>
       <c r="L60" s="8" t="inlineStr">
         <is>
+          <t>罗元泽</t>
+        </is>
+      </c>
+      <c r="M60" s="8" t="inlineStr">
+        <is>
+          <t>在职</t>
+        </is>
+      </c>
+      <c r="N60" s="8" t="inlineStr">
+        <is>
           <t>李敬</t>
         </is>
       </c>
-      <c r="M60" s="8" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
-      <c r="N60" s="8" t="inlineStr">
-        <is>
-          <t>李敬</t>
-        </is>
-      </c>
       <c r="O60" s="8" t="inlineStr">
         <is>
           <t>离职</t>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="P60" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>罗元泽</t>
         </is>
       </c>
       <c r="Q60" s="8" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="R60" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -5676,12 +5676,12 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202212004-S2</t>
+          <t>LZ-B-202212005</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>抖音-何光建执行和解协议</t>
+          <t>独家经纪合约-寇振宇（抖音，米奇）</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
@@ -5691,29 +5691,29 @@
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>上传电子档</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>23005</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>23005</t>
         </is>
       </c>
       <c r="J61" s="10" t="inlineStr"/>
       <c r="K61" s="11" t="inlineStr"/>
       <c r="L61" s="10" t="inlineStr">
         <is>
-          <t>罗元泽</t>
+          <t>李敬</t>
         </is>
       </c>
       <c r="M61" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N61" s="10" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="P61" s="10" t="inlineStr">
         <is>
-          <t>罗元泽</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q61" s="10" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="R61" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -5760,12 +5760,12 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202212005</t>
+          <t>LZ-B-202212005-S1</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合约-寇振宇（抖音，米奇）</t>
+          <t>补充协议-抖音，寇振宇</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>上传电子档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
@@ -5844,39 +5844,39 @@
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202212005-S1</t>
+          <t>LZ-B-202212009</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>补充协议-抖音，寇振宇</t>
+          <t>直播经纪合同（甜甜·丁佳稚）</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>23005</t>
+          <t>23710</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>23005</t>
+          <t>23710</t>
         </is>
       </c>
       <c r="J63" s="10" t="inlineStr"/>
       <c r="K63" s="11" t="inlineStr"/>
       <c r="L63" s="10" t="inlineStr">
         <is>
-          <t>李敬</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="M63" s="10" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="N63" s="10" t="inlineStr">
         <is>
-          <t>李敬</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="O63" s="10" t="inlineStr">
@@ -5928,69 +5928,57 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202212009</t>
+          <t>LZ-B-202301001</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>直播经纪合同（甜甜·丁佳稚）</t>
+          <t>贵阳主播尚雪独家经济合同</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>23710</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>23710</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr"/>
       <c r="K64" s="9" t="inlineStr"/>
       <c r="L64" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
-        </is>
-      </c>
-      <c r="M64" s="8" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
+          <t>龙栀炎</t>
+        </is>
+      </c>
+      <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
-        </is>
-      </c>
-      <c r="O64" s="8" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
+          <t>龙栀炎</t>
+        </is>
+      </c>
+      <c r="O64" s="8" t="inlineStr"/>
       <c r="P64" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
-        </is>
-      </c>
-      <c r="Q64" s="8" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
+          <t>龙栀炎</t>
+        </is>
+      </c>
+      <c r="Q64" s="8" t="inlineStr"/>
       <c r="R64" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -6012,57 +6000,69 @@
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202301001</t>
+          <t>LZ-B-202302002</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>贵阳主播尚雪独家经济合同</t>
+          <t>独家经纪约—李济民（抖音-李同学）</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>23705</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>23705</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="J65" s="10" t="inlineStr"/>
       <c r="K65" s="11" t="inlineStr"/>
       <c r="L65" s="10" t="inlineStr">
         <is>
-          <t>龙栀炎</t>
-        </is>
-      </c>
-      <c r="M65" s="10" t="inlineStr"/>
+          <t>李敬</t>
+        </is>
+      </c>
+      <c r="M65" s="10" t="inlineStr">
+        <is>
+          <t>离职</t>
+        </is>
+      </c>
       <c r="N65" s="10" t="inlineStr">
         <is>
-          <t>龙栀炎</t>
-        </is>
-      </c>
-      <c r="O65" s="10" t="inlineStr"/>
+          <t>李敬</t>
+        </is>
+      </c>
+      <c r="O65" s="10" t="inlineStr">
+        <is>
+          <t>离职</t>
+        </is>
+      </c>
       <c r="P65" s="10" t="inlineStr">
         <is>
-          <t>龙栀炎</t>
-        </is>
-      </c>
-      <c r="Q65" s="10" t="inlineStr"/>
+          <t>李家琪</t>
+        </is>
+      </c>
+      <c r="Q65" s="10" t="inlineStr">
+        <is>
+          <t>在职</t>
+        </is>
+      </c>
       <c r="R65" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -6084,12 +6084,12 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202302002</t>
+          <t>LZ-B-202302002-N</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>独家经纪约—李济民（抖音-李同学）</t>
+          <t>抖音-李济民（李同学）解除协议</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -6116,19 +6116,19 @@
       <c r="K66" s="9" t="inlineStr"/>
       <c r="L66" s="8" t="inlineStr">
         <is>
+          <t>罗元泽</t>
+        </is>
+      </c>
+      <c r="M66" s="8" t="inlineStr">
+        <is>
+          <t>在职</t>
+        </is>
+      </c>
+      <c r="N66" s="8" t="inlineStr">
+        <is>
           <t>李敬</t>
         </is>
       </c>
-      <c r="M66" s="8" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
-      <c r="N66" s="8" t="inlineStr">
-        <is>
-          <t>李敬</t>
-        </is>
-      </c>
       <c r="O66" s="8" t="inlineStr">
         <is>
           <t>离职</t>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="P66" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>罗元泽</t>
         </is>
       </c>
       <c r="Q66" s="8" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="R66" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -6168,49 +6168,49 @@
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202302002-N</t>
+          <t>LZ-B-202302003</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>抖音-李济民（李同学）解除协议</t>
+          <t>快手直播主播合作协议（叶月、快手、成都量子）</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>24140</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>24140</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="J67" s="10" t="inlineStr"/>
       <c r="K67" s="11" t="inlineStr"/>
       <c r="L67" s="10" t="inlineStr">
         <is>
-          <t>罗元泽</t>
+          <t>邹琦</t>
         </is>
       </c>
       <c r="M67" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N67" s="10" t="inlineStr">
         <is>
-          <t>李敬</t>
+          <t>邹琦</t>
         </is>
       </c>
       <c r="O67" s="10" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="P67" s="10" t="inlineStr">
         <is>
-          <t>罗元泽</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q67" s="10" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="R67" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -6252,39 +6252,39 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202302003</t>
+          <t>LZ-B-202302006</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>快手直播主播合作协议（叶月、快手、成都量子）</t>
+          <t>直播经纪合同（抖音·李丹丹·依晨）</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr"/>
       <c r="K68" s="9" t="inlineStr"/>
       <c r="L68" s="8" t="inlineStr">
         <is>
-          <t>邹琦</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="M68" s="8" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
-          <t>邹琦</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="O68" s="8" t="inlineStr">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202302006</t>
+          <t>LZ-B-202302007</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>直播经纪合同（抖音·李丹丹·依晨）</t>
+          <t>直播经纪合同（快手·刘桂羽·小羽）</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>24195</t>
+          <t>24197</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
         <is>
-          <t>24195</t>
+          <t>24197</t>
         </is>
       </c>
       <c r="J69" s="10" t="inlineStr"/>
@@ -6420,17 +6420,17 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202302007</t>
+          <t>LZ-B-202302008</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>直播经纪合同（快手·刘桂羽·小羽）</t>
+          <t>直播经纪合同（快手·代强·表弟）</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>24196</t>
         </is>
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>24196</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr"/>
@@ -6504,32 +6504,32 @@
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202302008</t>
+          <t>LZ-B-202303001</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>直播经纪合同（快手·代强·表弟）</t>
+          <t>主播经纪合同（袁雪梅-抖音-蝶梦）</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="J71" s="10" t="inlineStr"/>
@@ -6588,39 +6588,39 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202303001</t>
+          <t>LZ-B-202303002</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>主播经纪合同（袁雪梅-抖音-蝶梦）</t>
+          <t>独家经纪合同（唐婷）</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>24221</t>
+          <t>24201</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>24221</t>
+          <t>24201</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr"/>
       <c r="K72" s="9" t="inlineStr"/>
       <c r="L72" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>刘禹岐</t>
         </is>
       </c>
       <c r="M72" s="8" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="N72" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>刘禹岐</t>
         </is>
       </c>
       <c r="O72" s="8" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202303002</t>
+          <t>LZ-B-202303003</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（唐婷）</t>
+          <t>独家经纪合同（鲜惠）</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>24201</t>
+          <t>24223</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>24201</t>
+          <t>24223</t>
         </is>
       </c>
       <c r="J73" s="10" t="inlineStr"/>
@@ -6756,39 +6756,39 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202303003</t>
+          <t>LZ-B-202303004</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（鲜惠）</t>
+          <t>快手直播主播合作协议（叶月、宝宝不巴适、成都量子）</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>24223</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>24223</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr"/>
       <c r="K74" s="9" t="inlineStr"/>
       <c r="L74" s="8" t="inlineStr">
         <is>
-          <t>刘禹岐</t>
+          <t>邹琦</t>
         </is>
       </c>
       <c r="M74" s="8" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="N74" s="8" t="inlineStr">
         <is>
-          <t>刘禹岐</t>
+          <t>邹琦</t>
         </is>
       </c>
       <c r="O74" s="8" t="inlineStr">
@@ -6840,39 +6840,39 @@
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202303004</t>
+          <t>LZ-B-202303008</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>快手直播主播合作协议（叶月、宝宝不巴适、成都量子）</t>
+          <t>独家经纪合同（黄华敏）</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>24385</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>24385</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr"/>
       <c r="K75" s="11" t="inlineStr"/>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>邹琦</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="M75" s="10" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="N75" s="10" t="inlineStr">
         <is>
-          <t>邹琦</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="O75" s="10" t="inlineStr">
@@ -6924,17 +6924,17 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202303008</t>
+          <t>LZ-B-202303011</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（黄华敏）</t>
+          <t>独家经纪合同（陈露）</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>24385</t>
+          <t>24427</t>
         </is>
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>24385</t>
+          <t>24427</t>
         </is>
       </c>
       <c r="J76" s="8" t="inlineStr"/>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202303011</t>
+          <t>LZ-B-202303012</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（陈露）</t>
+          <t>快手直播主播合作协议（刘顺顺、快手、乐竞）</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
@@ -7023,24 +7023,24 @@
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>上传电子档</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>24426</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>24426</t>
         </is>
       </c>
       <c r="J77" s="10" t="inlineStr"/>
       <c r="K77" s="11" t="inlineStr"/>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>邱成业</t>
         </is>
       </c>
       <c r="M77" s="10" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="N77" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>邱成业</t>
         </is>
       </c>
       <c r="O77" s="10" t="inlineStr">
@@ -7092,39 +7092,39 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202303012</t>
+          <t>LZ-B-202303014</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>快手直播主播合作协议（刘顺顺、快手、乐竞）</t>
+          <t>独家经纪合同（抖音-洛洛-林小梅）</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>上传电子档</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>24462</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>24462</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr"/>
       <c r="K78" s="9" t="inlineStr"/>
       <c r="L78" s="8" t="inlineStr">
         <is>
-          <t>邱成业</t>
+          <t>曾兴林</t>
         </is>
       </c>
       <c r="M78" s="8" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="N78" s="8" t="inlineStr">
         <is>
-          <t>邱成业</t>
+          <t>曾兴林</t>
         </is>
       </c>
       <c r="O78" s="8" t="inlineStr">
@@ -7176,17 +7176,17 @@
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202303014</t>
+          <t>LZ-B-202306001</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（抖音-洛洛-林小梅）</t>
+          <t>独家经纪合同（李欣悦）</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
@@ -7196,19 +7196,19 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>24883</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>24883</t>
         </is>
       </c>
       <c r="J79" s="10" t="inlineStr"/>
       <c r="K79" s="11" t="inlineStr"/>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>曾兴林</t>
+          <t>刘禹岐</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="N79" s="10" t="inlineStr">
         <is>
-          <t>曾兴林</t>
+          <t>刘禹岐</t>
         </is>
       </c>
       <c r="O79" s="10" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202306001</t>
+          <t>LZ-B-202306002</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（李欣悦）</t>
+          <t>独家经纪合同（高杨）</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>24883</t>
+          <t>24884</t>
         </is>
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>24883</t>
+          <t>24884</t>
         </is>
       </c>
       <c r="J80" s="8" t="inlineStr"/>
@@ -7344,17 +7344,17 @@
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202306002</t>
+          <t>LZ-B-202306003</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（高杨）</t>
+          <t>独家经纪合同（廖婷婷）</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>24884</t>
+          <t>24888</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>24884</t>
+          <t>24888</t>
         </is>
       </c>
       <c r="J81" s="10" t="inlineStr"/>
@@ -7428,17 +7428,17 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202306003</t>
+          <t>LZ-B-202307006</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（廖婷婷）</t>
+          <t>独家经纪合同-(李丹丹)</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
@@ -7448,19 +7448,19 @@
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>24888</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>24888</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="J82" s="8" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="8" t="inlineStr">
         <is>
-          <t>刘禹岐</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="M82" s="8" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>刘禹岐</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="O82" s="8" t="inlineStr">
@@ -7512,17 +7512,17 @@
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202307006</t>
+          <t>LZ-B-202308003</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-(李丹丹)</t>
+          <t>独家经纪合同-(雍正)</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
@@ -7532,49 +7532,37 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>26612</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>26612</t>
         </is>
       </c>
       <c r="J83" s="10" t="inlineStr"/>
       <c r="K83" s="11" t="inlineStr"/>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
-        </is>
-      </c>
-      <c r="M83" s="10" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
+          <t>赵思敏</t>
+        </is>
+      </c>
+      <c r="M83" s="10" t="inlineStr"/>
       <c r="N83" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
-        </is>
-      </c>
-      <c r="O83" s="10" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
+          <t>赵思敏</t>
+        </is>
+      </c>
+      <c r="O83" s="10" t="inlineStr"/>
       <c r="P83" s="10" t="inlineStr">
         <is>
-          <t>李家琪</t>
-        </is>
-      </c>
-      <c r="Q83" s="10" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
+          <t>赵思敏</t>
+        </is>
+      </c>
+      <c r="Q83" s="10" t="inlineStr"/>
       <c r="R83" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -7596,57 +7584,69 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202308003</t>
+          <t>LZ-B-202309001</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-(雍正)</t>
+          <t>直播经纪合同（主持：刘昶堃）</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>26612</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>26612</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr"/>
       <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="8" t="inlineStr">
         <is>
-          <t>赵思敏</t>
-        </is>
-      </c>
-      <c r="M84" s="8" t="inlineStr"/>
+          <t>刘天桥</t>
+        </is>
+      </c>
+      <c r="M84" s="8" t="inlineStr">
+        <is>
+          <t>离职</t>
+        </is>
+      </c>
       <c r="N84" s="8" t="inlineStr">
         <is>
-          <t>赵思敏</t>
-        </is>
-      </c>
-      <c r="O84" s="8" t="inlineStr"/>
+          <t>刘天桥</t>
+        </is>
+      </c>
+      <c r="O84" s="8" t="inlineStr">
+        <is>
+          <t>离职</t>
+        </is>
+      </c>
       <c r="P84" s="8" t="inlineStr">
         <is>
-          <t>赵思敏</t>
-        </is>
-      </c>
-      <c r="Q84" s="8" t="inlineStr"/>
+          <t>李家琪</t>
+        </is>
+      </c>
+      <c r="Q84" s="8" t="inlineStr">
+        <is>
+          <t>在职</t>
+        </is>
+      </c>
       <c r="R84" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -7668,39 +7668,39 @@
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202309001</t>
+          <t>LZ-B-202401003</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>直播经纪合同（主持：刘昶堃）</t>
+          <t>独家经纪合约-（抖音，黎丹，卡蜜儿）</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>上传电子档</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>26815</t>
+          <t>27560</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>26815</t>
+          <t>27560</t>
         </is>
       </c>
       <c r="J85" s="10" t="inlineStr"/>
       <c r="K85" s="11" t="inlineStr"/>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>周宇航</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="N85" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>周宇航</t>
         </is>
       </c>
       <c r="O85" s="10" t="inlineStr">
@@ -7752,39 +7752,39 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202401003</t>
+          <t>LZ-B-202403004</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合约-（抖音，黎丹，卡蜜儿）</t>
+          <t>独家经纪合同-抖音-娜娜（马丽娜）</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2027-03-08</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>上传电子档</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>27560</t>
+          <t>28252</t>
         </is>
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>27560</t>
+          <t>28252</t>
         </is>
       </c>
       <c r="J86" s="8" t="inlineStr"/>
       <c r="K86" s="9" t="inlineStr"/>
       <c r="L86" s="8" t="inlineStr">
         <is>
-          <t>周宇航</t>
+          <t>邱成业</t>
         </is>
       </c>
       <c r="M86" s="8" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="N86" s="8" t="inlineStr">
         <is>
-          <t>周宇航</t>
+          <t>邱成业</t>
         </is>
       </c>
       <c r="O86" s="8" t="inlineStr">
@@ -7836,17 +7836,17 @@
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202403004</t>
+          <t>LZ-B-202403006</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-抖音-娜娜（马丽娜）</t>
+          <t>独家经纪合同--怡宝（周跃）</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>2027-03-08</t>
+          <t>2027-03-11</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
@@ -7856,19 +7856,19 @@
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>28252</t>
+          <t>28261</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>28252</t>
+          <t>28261</t>
         </is>
       </c>
       <c r="J87" s="10" t="inlineStr"/>
       <c r="K87" s="11" t="inlineStr"/>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>邱成业</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="N87" s="10" t="inlineStr">
         <is>
-          <t>邱成业</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="O87" s="10" t="inlineStr">
@@ -7920,17 +7920,17 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202403006</t>
+          <t>LZ-B-202403007</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同--怡宝（周跃）</t>
+          <t>独家经纪合同（户华波）</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>2027-03-11</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
@@ -7940,19 +7940,19 @@
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>28261</t>
+          <t>28272</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>28261</t>
+          <t>28272</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr"/>
       <c r="K88" s="9" t="inlineStr"/>
       <c r="L88" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>路钰忠</t>
         </is>
       </c>
       <c r="M88" s="8" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="N88" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>路钰忠</t>
         </is>
       </c>
       <c r="O88" s="8" t="inlineStr">
@@ -8004,17 +8004,17 @@
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202403007</t>
+          <t>LZ-B-202403010</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（户华波）</t>
+          <t>独家经纪合同--  溦溦（刘溦）</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
@@ -8024,12 +8024,12 @@
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>28272</t>
+          <t>28282</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>28272</t>
+          <t>28282</t>
         </is>
       </c>
       <c r="J89" s="10" t="inlineStr"/>
@@ -8088,12 +8088,12 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202403010</t>
+          <t>LZ-B-202403010-S1</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同--  溦溦（刘溦）</t>
+          <t>补充协议-刘溦</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -8120,19 +8120,15 @@
       <c r="K90" s="9" t="inlineStr"/>
       <c r="L90" s="8" t="inlineStr">
         <is>
+          <t>赵思敏</t>
+        </is>
+      </c>
+      <c r="M90" s="8" t="inlineStr"/>
+      <c r="N90" s="8" t="inlineStr">
+        <is>
           <t>路钰忠</t>
         </is>
       </c>
-      <c r="M90" s="8" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
-      <c r="N90" s="8" t="inlineStr">
-        <is>
-          <t>路钰忠</t>
-        </is>
-      </c>
       <c r="O90" s="8" t="inlineStr">
         <is>
           <t>离职</t>
@@ -8140,17 +8136,13 @@
       </c>
       <c r="P90" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
-        </is>
-      </c>
-      <c r="Q90" s="8" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
+          <t>赵思敏</t>
+        </is>
+      </c>
+      <c r="Q90" s="8" t="inlineStr"/>
       <c r="R90" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -8172,45 +8164,49 @@
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202403010-S1</t>
+          <t>LZ-B-202403011</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>补充协议-刘溦</t>
+          <t>独家经纪合同-tiktok-崽崽（王洁）</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>2027-03-06</t>
+          <t>2027-03-11</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>28282</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>28282</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="J91" s="10" t="inlineStr"/>
       <c r="K91" s="11" t="inlineStr"/>
       <c r="L91" s="10" t="inlineStr">
         <is>
-          <t>赵思敏</t>
-        </is>
-      </c>
-      <c r="M91" s="10" t="inlineStr"/>
+          <t>刘天桥</t>
+        </is>
+      </c>
+      <c r="M91" s="10" t="inlineStr">
+        <is>
+          <t>离职</t>
+        </is>
+      </c>
       <c r="N91" s="10" t="inlineStr">
         <is>
-          <t>路钰忠</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="O91" s="10" t="inlineStr">
@@ -8220,13 +8216,17 @@
       </c>
       <c r="P91" s="10" t="inlineStr">
         <is>
-          <t>赵思敏</t>
-        </is>
-      </c>
-      <c r="Q91" s="10" t="inlineStr"/>
+          <t>李家琪</t>
+        </is>
+      </c>
+      <c r="Q91" s="10" t="inlineStr">
+        <is>
+          <t>在职</t>
+        </is>
+      </c>
       <c r="R91" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -8248,17 +8248,17 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202403011</t>
+          <t>LZ-B-202403012</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-tiktok-崽崽（王洁）</t>
+          <t>主播经纪合同-tiktok-（黄朴铃风）</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>2027-03-11</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>28298</t>
+          <t>28331</t>
         </is>
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>28298</t>
+          <t>28331</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr"/>
@@ -8332,17 +8332,17 @@
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202403012</t>
+          <t>LZ-B-202404001</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>主播经纪合同-tiktok-（黄朴铃风）</t>
+          <t>独家经纪合同-tiktok-TiTi（惠番娟）</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>2027-03-31</t>
+          <t>2027-03-07</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>28331</t>
+          <t>28340</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
         <is>
-          <t>28331</t>
+          <t>28340</t>
         </is>
       </c>
       <c r="J93" s="10" t="inlineStr"/>
@@ -8416,17 +8416,17 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202404001</t>
+          <t>LZ-B-202406001</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-tiktok-TiTi（惠番娟）</t>
+          <t>独家经纪合同（tiktok uu ）孟晓艺</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>2027-03-07</t>
+          <t>2027-05-31</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
@@ -8436,19 +8436,19 @@
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>28340</t>
+          <t>28724</t>
         </is>
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>28340</t>
+          <t>28724</t>
         </is>
       </c>
       <c r="J94" s="8" t="inlineStr"/>
       <c r="K94" s="9" t="inlineStr"/>
       <c r="L94" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>邱成业</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="N94" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>邱成业</t>
         </is>
       </c>
       <c r="O94" s="8" t="inlineStr">
@@ -8500,17 +8500,17 @@
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202406001</t>
+          <t>LZ-B-202408001</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（tiktok uu ）孟晓艺</t>
+          <t>独家经纪合同-tiktok- 泡泡（廖丹）</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>2027-05-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -8520,19 +8520,19 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>28724</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
         <is>
-          <t>28724</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="J95" s="10" t="inlineStr"/>
       <c r="K95" s="11" t="inlineStr"/>
       <c r="L95" s="10" t="inlineStr">
         <is>
-          <t>邱成业</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="M95" s="10" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="N95" s="10" t="inlineStr">
         <is>
-          <t>邱成业</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="O95" s="10" t="inlineStr">
@@ -8584,17 +8584,17 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>LZ-B-202408001</t>
+          <t>NP-JS-20210520-S1</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-tiktok- 泡泡（廖丹）</t>
+          <t>NP-JS-20210520-S1-《独家经纪合同》之补充协议（二）-厚翰和金泰相-0-20211203</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
@@ -8602,41 +8602,33 @@
           <t>归档</t>
         </is>
       </c>
-      <c r="H96" s="8" t="inlineStr">
-        <is>
-          <t>28996</t>
-        </is>
-      </c>
-      <c r="I96" s="8" t="inlineStr">
-        <is>
-          <t>28996</t>
-        </is>
-      </c>
+      <c r="H96" s="8" t="n"/>
+      <c r="I96" s="8" t="n"/>
       <c r="J96" s="8" t="inlineStr"/>
       <c r="K96" s="9" t="inlineStr"/>
       <c r="L96" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N96" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="O96" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P96" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="Q96" s="8" t="inlineStr">
@@ -8646,7 +8638,7 @@
       </c>
       <c r="R96" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -8668,12 +8660,12 @@
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1</t>
+          <t>NP-JS-20210520-S1-S1</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1-《独家经纪合同》之补充协议（二）-厚翰和金泰相-0-20211203</t>
+          <t>合同主体变更四方协议-厚翰金泰相栗金闪金</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
@@ -8683,7 +8675,7 @@
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>法务确认</t>
         </is>
       </c>
       <c r="H97" s="10" t="n"/>
@@ -8744,12 +8736,12 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1-S1</t>
+          <t>NP-JS-20210520-S1-S2</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>合同主体变更四方协议-厚翰金泰相栗金闪金</t>
+          <t>补充账户信息-三方协议-Doinb厚翰闪金</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
@@ -8759,7 +8751,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>法务确认</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H98" s="8" t="n"/>
@@ -8768,29 +8760,29 @@
       <c r="K98" s="9" t="inlineStr"/>
       <c r="L98" s="8" t="inlineStr">
         <is>
+          <t>梁浩嘉</t>
+        </is>
+      </c>
+      <c r="M98" s="8" t="inlineStr">
+        <is>
+          <t>离职</t>
+        </is>
+      </c>
+      <c r="N98" s="8" t="inlineStr">
+        <is>
           <t>彭敏</t>
         </is>
       </c>
-      <c r="M98" s="8" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
-      <c r="N98" s="8" t="inlineStr">
+      <c r="O98" s="8" t="inlineStr">
+        <is>
+          <t>在职</t>
+        </is>
+      </c>
+      <c r="P98" s="8" t="inlineStr">
         <is>
           <t>彭敏</t>
         </is>
       </c>
-      <c r="O98" s="8" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
-      <c r="P98" s="8" t="inlineStr">
-        <is>
-          <t>彭敏</t>
-        </is>
-      </c>
       <c r="Q98" s="8" t="inlineStr">
         <is>
           <t>在职</t>
@@ -8798,7 +8790,7 @@
       </c>
       <c r="R98" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,更新为合同执行人</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8812,7 @@
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1-S2</t>
+          <t>NP-JS-20210520-S1-S3</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
@@ -8835,7 +8827,7 @@
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>法务确认</t>
         </is>
       </c>
       <c r="H99" s="10" t="n"/>
@@ -8844,12 +8836,12 @@
       <c r="K99" s="11" t="inlineStr"/>
       <c r="L99" s="10" t="inlineStr">
         <is>
-          <t>梁浩嘉</t>
+          <t>胡浥盟</t>
         </is>
       </c>
       <c r="M99" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N99" s="10" t="inlineStr">
@@ -8864,7 +8856,7 @@
       </c>
       <c r="P99" s="10" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>胡浥盟</t>
         </is>
       </c>
       <c r="Q99" s="10" t="inlineStr">
@@ -8874,7 +8866,7 @@
       </c>
       <c r="R99" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,更新为合同执行人</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -8896,12 +8888,12 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1-S3</t>
+          <t>NP-JS-20210520-S1-S4</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>补充账户信息-三方协议-Doinb厚翰闪金</t>
+          <t>合同主体变更四方协议-厚翰金泰相闪金浅擎</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
@@ -8920,7 +8912,7 @@
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="8" t="inlineStr">
         <is>
-          <t>胡浥盟</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="M100" s="8" t="inlineStr">
@@ -8940,7 +8932,7 @@
       </c>
       <c r="P100" s="8" t="inlineStr">
         <is>
-          <t>胡浥盟</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="Q100" s="8" t="inlineStr">
@@ -8972,12 +8964,12 @@
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1-S4</t>
+          <t>NP-JS-20210520-S1-S5</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>合同主体变更四方协议-厚翰金泰相闪金浅擎</t>
+          <t>斗鱼直播一部游戏组-金泰相-《独家经纪合同》之补充协议（三）（主播昵称：金咕咕金咕咕doinb ）(主播姓名：金泰相 )</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
@@ -8987,7 +8979,7 @@
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>法务确认</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H101" s="10" t="n"/>
@@ -9048,22 +9040,22 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1-S5</t>
+          <t>NP-JS-202107-N</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>斗鱼直播一部游戏组-金泰相-《独家经纪合同》之补充协议（三）（主播昵称：金咕咕金咕咕doinb ）(主播姓名：金泰相 )</t>
+          <t>厚翰—主播姚琳解约协议</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H102" s="8" t="n"/>
@@ -9072,27 +9064,27 @@
       <c r="K102" s="9" t="inlineStr"/>
       <c r="L102" s="8" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>黄芷萱</t>
         </is>
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N102" s="8" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>周玉婷</t>
         </is>
       </c>
       <c r="O102" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P102" s="8" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q102" s="8" t="inlineStr">
@@ -9102,7 +9094,7 @@
       </c>
       <c r="R102" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -9124,17 +9116,17 @@
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>NP-JS-202107-N</t>
+          <t>QS-B-202306001</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>厚翰—主播姚琳解约协议</t>
+          <t>抖音娱乐主播-于格格（鱼鱼）独家经纪约</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
@@ -9142,33 +9134,41 @@
           <t>归档</t>
         </is>
       </c>
-      <c r="H103" s="10" t="n"/>
-      <c r="I103" s="10" t="n"/>
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>24887</t>
+        </is>
+      </c>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>24887</t>
+        </is>
+      </c>
       <c r="J103" s="10" t="inlineStr"/>
       <c r="K103" s="11" t="inlineStr"/>
       <c r="L103" s="10" t="inlineStr">
         <is>
-          <t>黄芷萱</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N103" s="10" t="inlineStr">
         <is>
-          <t>周玉婷</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="O103" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P103" s="10" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="Q103" s="10" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="R103" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -9200,59 +9200,59 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>QS-B-202306001</t>
+          <t>QS-B-202308028</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>抖音娱乐主播-于格格（鱼鱼）独家经纪约</t>
+          <t>【擎狮合同】米米主播经纪合同</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>法务确认</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>26788</t>
         </is>
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>26788</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr"/>
       <c r="K104" s="9" t="inlineStr"/>
       <c r="L104" s="8" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>张靖</t>
         </is>
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N104" s="8" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>张靖</t>
         </is>
       </c>
       <c r="O104" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P104" s="8" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q104" s="8" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="R104" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -9284,17 +9284,17 @@
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>QS-B-202308028</t>
+          <t>QS-O-202307001</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>【擎狮合同】米米主播经纪合同</t>
+          <t>渠道经纪合作协议-苏杰</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
@@ -9304,39 +9304,39 @@
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>26788</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr">
         <is>
-          <t>26788</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="J105" s="10" t="inlineStr"/>
       <c r="K105" s="11" t="inlineStr"/>
       <c r="L105" s="10" t="inlineStr">
         <is>
-          <t>张靖</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="M105" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N105" s="10" t="inlineStr">
         <is>
-          <t>张靖</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="O105" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P105" s="10" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="Q105" s="10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="R105" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>QS-O-202307001</t>
+          <t>QS-O-202310001</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
@@ -9378,12 +9378,12 @@
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>法务确认</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
@@ -9452,17 +9452,17 @@
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>QS-O-202310001</t>
+          <t>SHSY-B-202404003</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>渠道经纪合作协议-苏杰</t>
+          <t>独家经纪合同-tiktok- 小奕（王秋涵）</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2027-04-11</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
@@ -9472,39 +9472,39 @@
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>28355</t>
         </is>
       </c>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>28355</t>
         </is>
       </c>
       <c r="J107" s="10" t="inlineStr"/>
       <c r="K107" s="11" t="inlineStr"/>
       <c r="L107" s="10" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="M107" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N107" s="10" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="O107" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P107" s="10" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q107" s="10" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="R107" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -9536,17 +9536,17 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202404003</t>
+          <t>SHSY-B-202404004</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-tiktok- 小奕（王秋涵）</t>
+          <t>独家经纪合同-tiktok-ka ka（旦真泽郎）</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>2027-04-11</t>
+          <t>2027-04-02</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>28355</t>
+          <t>28345</t>
         </is>
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>28355</t>
+          <t>28345</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr"/>
@@ -9620,17 +9620,17 @@
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202404004</t>
+          <t>SHSY-B-202407002</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-tiktok-ka ka（旦真泽郎）</t>
+          <t>主播经纪合同-tiktok-（黄志伟）</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>2027-04-02</t>
+          <t>2027-06-30</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
@@ -9640,12 +9640,12 @@
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="J109" s="10" t="inlineStr"/>
@@ -9704,17 +9704,17 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202407002</t>
+          <t>SHSY-B-202407003</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>主播经纪合同-tiktok-（黄志伟）</t>
+          <t>独家经纪合同-tiktok- 邓雅兰（小九）</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
-          <t>2027-06-30</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
@@ -9724,19 +9724,19 @@
       </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>28881</t>
+          <t>28924</t>
         </is>
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>28881</t>
+          <t>28924</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr"/>
       <c r="K110" s="9" t="inlineStr"/>
       <c r="L110" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>路钰忠</t>
         </is>
       </c>
       <c r="M110" s="8" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="N110" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>路钰忠</t>
         </is>
       </c>
       <c r="O110" s="8" t="inlineStr">
@@ -9788,12 +9788,12 @@
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202407003</t>
+          <t>SHSY-B-202407004</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-tiktok- 邓雅兰（小九）</t>
+          <t>主播经纪合同-tiktok-（吕思盟）</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
@@ -9808,19 +9808,19 @@
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>28924</t>
+          <t>28925</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr">
         <is>
-          <t>28924</t>
+          <t>28925</t>
         </is>
       </c>
       <c r="J111" s="10" t="inlineStr"/>
       <c r="K111" s="11" t="inlineStr"/>
       <c r="L111" s="10" t="inlineStr">
         <is>
-          <t>路钰忠</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="M111" s="10" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="N111" s="10" t="inlineStr">
         <is>
-          <t>路钰忠</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="O111" s="10" t="inlineStr">
@@ -9872,39 +9872,39 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202407004</t>
+          <t>SHSY-B-202408003</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>主播经纪合同-tiktok-（吕思盟）</t>
+          <t>独家经纪协议-抖音-李金阳</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2027-08-14</t>
         </is>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>28992</t>
         </is>
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>28992</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr"/>
       <c r="K112" s="9" t="inlineStr"/>
       <c r="L112" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>宋进</t>
         </is>
       </c>
       <c r="M112" s="8" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="N112" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>宋进</t>
         </is>
       </c>
       <c r="O112" s="8" t="inlineStr">
@@ -9956,12 +9956,12 @@
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202408003</t>
+          <t>SHSY-B-202408003-N</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-李金阳</t>
+          <t>解除协议-抖音-李金阳</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
@@ -9988,7 +9988,7 @@
       <c r="K113" s="11" t="inlineStr"/>
       <c r="L113" s="10" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>乔颖</t>
         </is>
       </c>
       <c r="M113" s="10" t="inlineStr">
@@ -10040,12 +10040,12 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202408003-N</t>
+          <t>SHSY-B-202408004</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>解除协议-抖音-李金阳</t>
+          <t>独家经纪协议-抖音-曾一凡</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
@@ -10055,24 +10055,24 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H114" s="8" t="inlineStr">
         <is>
-          <t>28992</t>
+          <t>28994</t>
         </is>
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>28992</t>
+          <t>28994</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr"/>
       <c r="K114" s="9" t="inlineStr"/>
       <c r="L114" s="8" t="inlineStr">
         <is>
-          <t>乔颖</t>
+          <t>宋进</t>
         </is>
       </c>
       <c r="M114" s="8" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202408004</t>
+          <t>SHSY-B-202408004-N</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-曾一凡</t>
+          <t>解除协议-抖音-曾一凡</t>
         </is>
       </c>
       <c r="F115" s="10" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
@@ -10156,7 +10156,7 @@
       <c r="K115" s="11" t="inlineStr"/>
       <c r="L115" s="10" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>乔颖</t>
         </is>
       </c>
       <c r="M115" s="10" t="inlineStr">
@@ -10208,39 +10208,39 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202408004-N</t>
+          <t>SHSY-B-202408006</t>
         </is>
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>解除协议-抖音-曾一凡</t>
+          <t>独家经纪合同-tiktok- 泡泡（廖丹）</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
-          <t>2027-08-14</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>上传电子档</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
         <is>
-          <t>28994</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>28994</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr"/>
       <c r="K116" s="9" t="inlineStr"/>
       <c r="L116" s="8" t="inlineStr">
         <is>
-          <t>乔颖</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="M116" s="8" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="N116" s="8" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="O116" s="8" t="inlineStr">
@@ -10292,39 +10292,39 @@
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202408006</t>
+          <t>SHSY-B-202408016</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-tiktok- 泡泡（廖丹）</t>
+          <t>独家经纪协议-抖音-胥梦娇</t>
         </is>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2027-08-26</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>上传电子档</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>28996</t>
+          <t>29116</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr">
         <is>
-          <t>28996</t>
+          <t>29116</t>
         </is>
       </c>
       <c r="J117" s="10" t="inlineStr"/>
       <c r="K117" s="11" t="inlineStr"/>
       <c r="L117" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>宋进</t>
         </is>
       </c>
       <c r="M117" s="10" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="N117" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>宋进</t>
         </is>
       </c>
       <c r="O117" s="10" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202408016</t>
+          <t>SHSY-B-202408019</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-胥梦娇</t>
+          <t>独家经济协议-抖音-颜亚欣</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
-          <t>2027-08-26</t>
+          <t>2027-09-14</t>
         </is>
       </c>
       <c r="G118" s="8" t="inlineStr">
@@ -10396,12 +10396,12 @@
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>29116</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>29116</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr"/>
@@ -10460,17 +10460,17 @@
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202408019</t>
+          <t>SHSY-B-202409002</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>独家经济协议-抖音-颜亚欣</t>
+          <t>独家经纪协议-抖音-颜亚欣</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>2027-09-14</t>
+          <t>2027-08-29</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -10544,17 +10544,17 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202409002</t>
+          <t>SHSY-B-202409003</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-颜亚欣</t>
+          <t>独家经纪协议-抖音-赵丹</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
-          <t>2027-08-29</t>
+          <t>2027-09-10</t>
         </is>
       </c>
       <c r="G120" s="8" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>29147</t>
+          <t>29174</t>
         </is>
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>29147</t>
+          <t>29174</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr"/>
@@ -10628,39 +10628,39 @@
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202409003</t>
+          <t>SHSY-B-202409005</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-赵丹</t>
+          <t>主播经纪合同-tiktok-（吕思盟）</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>2027-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>29174</t>
+          <t>28925</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
         <is>
-          <t>29174</t>
+          <t>28925</t>
         </is>
       </c>
       <c r="J121" s="10" t="inlineStr"/>
       <c r="K121" s="11" t="inlineStr"/>
       <c r="L121" s="10" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>路钰忠</t>
         </is>
       </c>
       <c r="M121" s="10" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="N121" s="10" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>路钰忠</t>
         </is>
       </c>
       <c r="O121" s="10" t="inlineStr">
@@ -10712,39 +10712,39 @@
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202409005</t>
+          <t>SHSY-B-202409009</t>
         </is>
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>主播经纪合同-tiktok-（吕思盟）</t>
+          <t>独家经纪协议-抖音-王瑶</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2027-09-26</t>
         </is>
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>上传电子档</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>29223</t>
         </is>
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>29223</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr"/>
       <c r="K122" s="9" t="inlineStr"/>
       <c r="L122" s="8" t="inlineStr">
         <is>
-          <t>路钰忠</t>
+          <t>乔颖</t>
         </is>
       </c>
       <c r="M122" s="8" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="N122" s="8" t="inlineStr">
         <is>
-          <t>路钰忠</t>
+          <t>乔颖</t>
         </is>
       </c>
       <c r="O122" s="8" t="inlineStr">
@@ -10796,17 +10796,17 @@
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202409009</t>
+          <t>SHSY-B-202410003</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-王瑶</t>
+          <t>独家经纪协议-抖音-钟佳芮</t>
         </is>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>2027-09-26</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>29354</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>29354</t>
         </is>
       </c>
       <c r="J123" s="10" t="inlineStr"/>
@@ -10880,59 +10880,59 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202410003</t>
+          <t>VMSB-B-202501002</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-钟佳芮</t>
+          <t>独家经纪合同（En En）</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>上传电子档</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H124" s="8" t="inlineStr">
         <is>
-          <t>29354</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>29354</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr"/>
       <c r="K124" s="9" t="inlineStr"/>
       <c r="L124" s="8" t="inlineStr">
         <is>
-          <t>乔颖</t>
+          <t>Wei Shi (Jessy) Chang</t>
         </is>
       </c>
       <c r="M124" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N124" s="8" t="inlineStr">
         <is>
-          <t>乔颖</t>
+          <t>Wei Shi (Jessy) Chang</t>
         </is>
       </c>
       <c r="O124" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P124" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>Wei Shi (Jessy) Chang</t>
         </is>
       </c>
       <c r="Q124" s="8" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="R124" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -10964,12 +10964,12 @@
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202501002</t>
+          <t>VMSB-B-202501002-N</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（En En）</t>
+          <t>艺人解除协议（双语）Tan Ru Enn</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
@@ -11048,17 +11048,17 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202501002-N</t>
+          <t>VMSB-B-202504003</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>艺人解除协议（双语）Tan Ru Enn</t>
+          <t>独家经纪合同（Chia Qi Er）</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="G126" s="8" t="inlineStr">
@@ -11068,19 +11068,19 @@
       </c>
       <c r="H126" s="8" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>29216</t>
         </is>
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>29216</t>
         </is>
       </c>
       <c r="J126" s="8" t="inlineStr"/>
       <c r="K126" s="9" t="inlineStr"/>
       <c r="L126" s="8" t="inlineStr">
         <is>
-          <t>Wei Shi (Jessy) Chang</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="M126" s="8" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="N126" s="8" t="inlineStr">
         <is>
-          <t>Wei Shi (Jessy) Chang</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="O126" s="8" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P126" s="8" t="inlineStr">
         <is>
-          <t>Wei Shi (Jessy) Chang</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="Q126" s="8" t="inlineStr">
@@ -11132,12 +11132,12 @@
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202504003</t>
+          <t>VMSB-B-202504004</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Chia Qi Er）</t>
+          <t>独家经纪合同（Ngoi Suen Jia）</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>29216</t>
+          <t>29385</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
         <is>
-          <t>29216</t>
+          <t>29385</t>
         </is>
       </c>
       <c r="J127" s="10" t="inlineStr"/>
@@ -11216,17 +11216,17 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202504004</t>
+          <t>VMSB-B-202504005</t>
         </is>
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Ngoi Suen Jia）</t>
+          <t>独家经纪合同（CHIN ROU JING) Joanne</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
         <is>
-          <t>2027-03-31</t>
+          <t>2027-06-22</t>
         </is>
       </c>
       <c r="G128" s="8" t="inlineStr">
@@ -11236,19 +11236,19 @@
       </c>
       <c r="H128" s="8" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="J128" s="8" t="inlineStr"/>
       <c r="K128" s="9" t="inlineStr"/>
       <c r="L128" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="M128" s="8" t="inlineStr">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="N128" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="O128" s="8" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="P128" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="Q128" s="8" t="inlineStr">
@@ -11300,32 +11300,32 @@
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202504005</t>
+          <t>VMSB-B-202504006</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（CHIN ROU JING) Joanne</t>
+          <t>独家经纪合同（CHEONG LEI KENG) Elsa</t>
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>2027-06-22</t>
+          <t>2027-04-23</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="J129" s="10" t="inlineStr"/>
@@ -11384,32 +11384,32 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202504006</t>
+          <t>VMSB-B-202504008</t>
         </is>
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（CHEONG LEI KENG) Elsa</t>
+          <t>独家经纪合同（WENDY CALANDRIA TAN) Emma</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
         <is>
-          <t>2027-04-23</t>
+          <t>2027-04-24</t>
         </is>
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H130" s="8" t="inlineStr">
         <is>
-          <t>28947</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>28947</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr"/>
@@ -11468,17 +11468,17 @@
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202504008</t>
+          <t>VMSB-B-202504009</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（WENDY CALANDRIA TAN) Emma</t>
+          <t>独家经纪合同（Chong Shun Yee Vinette）</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>2027-04-24</t>
+          <t>2027-04-13</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
@@ -11488,19 +11488,19 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>29848</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>29848</t>
         </is>
       </c>
       <c r="J131" s="10" t="inlineStr"/>
       <c r="K131" s="11" t="inlineStr"/>
       <c r="L131" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="M131" s="10" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="N131" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="O131" s="10" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="P131" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="Q131" s="10" t="inlineStr">
@@ -11552,17 +11552,17 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202504009</t>
+          <t>VMSB-B-202504016</t>
         </is>
       </c>
       <c r="E132" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Chong Shun Yee Vinette）</t>
+          <t>独家经纪合同（Candy Chan Jia Tong）</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
         <is>
-          <t>2027-04-13</t>
+          <t>2027-04-20</t>
         </is>
       </c>
       <c r="G132" s="8" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="H132" s="8" t="inlineStr">
         <is>
-          <t>29848</t>
+          <t>29854</t>
         </is>
       </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>29848</t>
+          <t>29854</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr"/>
@@ -11636,17 +11636,17 @@
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202504016</t>
+          <t>VMSB-B-202506001</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Candy Chan Jia Tong）</t>
+          <t>独家经纪合同（Edison）</t>
         </is>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>2027-04-20</t>
+          <t>2027-06-10</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
@@ -11656,39 +11656,39 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>29854</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr">
         <is>
-          <t>29854</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="J133" s="10" t="inlineStr"/>
       <c r="K133" s="11" t="inlineStr"/>
       <c r="L133" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>Sze Yu Lim</t>
         </is>
       </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N133" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>Sze Yu Lim</t>
         </is>
       </c>
       <c r="O133" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P133" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q133" s="10" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="R133" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -11720,59 +11720,59 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202506001</t>
+          <t>VMSB-B-202508002</t>
         </is>
       </c>
       <c r="E134" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Edison）</t>
+          <t>独家经纪合同（Tang Huan Ting）yaya</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>2027-06-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H134" s="8" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="J134" s="8" t="inlineStr"/>
       <c r="K134" s="9" t="inlineStr"/>
       <c r="L134" s="8" t="inlineStr">
         <is>
-          <t>Sze Yu Lim</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="M134" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N134" s="8" t="inlineStr">
         <is>
-          <t>Sze Yu Lim</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="O134" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P134" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="Q134" s="8" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="R134" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202508002</t>
+          <t>VMSB-B-202508003</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Tang Huan Ting）yaya</t>
+          <t>独家经纪合同（Lee Hsueh En）Snowie</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
@@ -11819,17 +11819,17 @@
       </c>
       <c r="G135" s="10" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>30283</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
         <is>
-          <t>30283</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="J135" s="10" t="inlineStr"/>
@@ -11888,12 +11888,12 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202508003</t>
+          <t>VMSB-B-202508004</t>
         </is>
       </c>
       <c r="E136" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Lee Hsueh En）Snowie</t>
+          <t>独家经纪合同（Chow Si Wei）Bella</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="H136" s="8" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="J136" s="8" t="inlineStr"/>
@@ -11972,17 +11972,17 @@
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202508004</t>
+          <t>VMSB-B-202509002</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Chow Si Wei）Bella</t>
+          <t>独家经纪合同（Tang Khye Rine）Cat</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2027-08-31</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>30281</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
         <is>
-          <t>30281</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="J137" s="10" t="inlineStr"/>
@@ -12056,17 +12056,17 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202509002</t>
+          <t>VMSB-B-202509005</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Tang Khye Rine）Cat</t>
+          <t>独家经纪合同 (Chan Jia wen)</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
-          <t>2027-08-31</t>
+          <t>2027-09-08</t>
         </is>
       </c>
       <c r="G138" s="8" t="inlineStr">
@@ -12076,12 +12076,12 @@
       </c>
       <c r="H138" s="8" t="inlineStr">
         <is>
-          <t>30514</t>
+          <t>30677</t>
         </is>
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
-          <t>30514</t>
+          <t>30677</t>
         </is>
       </c>
       <c r="J138" s="8" t="inlineStr"/>
@@ -12140,32 +12140,32 @@
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202509005</t>
+          <t>VMSB-B-202510005</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同 (Chan Jia wen)</t>
+          <t>主播租赁协议（EMMA）</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>2027-09-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>30677</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
         <is>
-          <t>30677</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="J139" s="10" t="inlineStr"/>
@@ -12224,17 +12224,17 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202510005</t>
+          <t>VMSB-B-202511001</t>
         </is>
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>主播租赁协议（EMMA）</t>
+          <t>独家经纪合同（Yaw Mei Yen）Peanuat</t>
         </is>
       </c>
       <c r="F140" s="8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2027-10-31</t>
         </is>
       </c>
       <c r="G140" s="8" t="inlineStr">
@@ -12244,12 +12244,12 @@
       </c>
       <c r="H140" s="8" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>30860</t>
         </is>
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>30860</t>
         </is>
       </c>
       <c r="J140" s="8" t="inlineStr"/>
@@ -12308,32 +12308,32 @@
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202511001</t>
+          <t>VMSB-B-202511002</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Yaw Mei Yen）Peanuat</t>
+          <t>独家经纪合同（Kang Chung Hong- Jden）</t>
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>2027-10-31</t>
+          <t>2027-11-22</t>
         </is>
       </c>
       <c r="G141" s="10" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>30860</t>
+          <t>30859</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>30860</t>
+          <t>30859</t>
         </is>
       </c>
       <c r="J141" s="10" t="inlineStr"/>
@@ -12392,17 +12392,17 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202511002</t>
+          <t>VMSB-B-202511004</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Kang Chung Hong- Jden）</t>
+          <t>独家经纪合同（Chewy）</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
         <is>
-          <t>2027-11-22</t>
+          <t>2027-11-09</t>
         </is>
       </c>
       <c r="G142" s="8" t="inlineStr">
@@ -12412,19 +12412,19 @@
       </c>
       <c r="H142" s="8" t="inlineStr">
         <is>
-          <t>30859</t>
+          <t>31032</t>
         </is>
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>30859</t>
+          <t>31032</t>
         </is>
       </c>
       <c r="J142" s="8" t="inlineStr"/>
       <c r="K142" s="9" t="inlineStr"/>
       <c r="L142" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="M142" s="8" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="N142" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="O142" s="8" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="P142" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="Q142" s="8" t="inlineStr">
@@ -12476,12 +12476,12 @@
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202511004</t>
+          <t>VMSB-B-202511005</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Chewy）</t>
+          <t>独家经纪合同（Nini）</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>31032</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
         <is>
-          <t>31032</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="J143" s="10" t="inlineStr"/>
@@ -12560,12 +12560,12 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202511005</t>
+          <t>VMSB-B-202511006</t>
         </is>
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Nini）</t>
+          <t>独家经纪合同</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="H144" s="8" t="inlineStr">
         <is>
-          <t>31029</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
-          <t>31029</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="J144" s="8" t="inlineStr"/>
@@ -12644,12 +12644,12 @@
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202511006</t>
+          <t>VMSB-B-202511007</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同</t>
+          <t>独家经纪合同（Mika）</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="H145" s="10" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>31030</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>31030</t>
         </is>
       </c>
       <c r="J145" s="10" t="inlineStr"/>
@@ -12728,12 +12728,12 @@
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202511007</t>
+          <t>VMSB-B-202512001</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Mika）</t>
+          <t>独家经纪合同</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr">
@@ -12748,12 +12748,12 @@
       </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
-          <t>31030</t>
+          <t>31075</t>
         </is>
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
-          <t>31030</t>
+          <t>31075</t>
         </is>
       </c>
       <c r="J146" s="8" t="inlineStr"/>
@@ -12812,17 +12812,17 @@
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202512001</t>
+          <t>VMSB-B-202601002</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同</t>
+          <t>独家经纪合同（CHEONG LEI KENG) Elsa</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>2027-11-09</t>
+          <t>2028-01-05</t>
         </is>
       </c>
       <c r="G147" s="10" t="inlineStr">
@@ -12832,19 +12832,19 @@
       </c>
       <c r="H147" s="10" t="inlineStr">
         <is>
-          <t>31075</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
         <is>
-          <t>31075</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="J147" s="10" t="inlineStr"/>
       <c r="K147" s="11" t="inlineStr"/>
       <c r="L147" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="M147" s="10" t="inlineStr">
@@ -12854,7 +12854,7 @@
       </c>
       <c r="N147" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="O147" s="10" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P147" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="Q147" s="10" t="inlineStr">
@@ -12896,17 +12896,17 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202601002</t>
+          <t>VMSB-O-202410001</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（CHEONG LEI KENG) Elsa</t>
+          <t>独家经纪合同 （WONG CHAI NI）Kelly</t>
         </is>
       </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
-          <t>2028-01-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G148" s="8" t="inlineStr">
@@ -12914,41 +12914,33 @@
           <t>归档</t>
         </is>
       </c>
-      <c r="H148" s="8" t="inlineStr">
-        <is>
-          <t>28947</t>
-        </is>
-      </c>
-      <c r="I148" s="8" t="inlineStr">
-        <is>
-          <t>28947</t>
-        </is>
-      </c>
+      <c r="H148" s="8" t="inlineStr"/>
+      <c r="I148" s="8" t="inlineStr"/>
       <c r="J148" s="8" t="inlineStr"/>
       <c r="K148" s="9" t="inlineStr"/>
       <c r="L148" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>YU JING YI</t>
         </is>
       </c>
       <c r="M148" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N148" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>YU JING YI</t>
         </is>
       </c>
       <c r="O148" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P148" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q148" s="8" t="inlineStr">
@@ -12958,7 +12950,7 @@
       </c>
       <c r="R148" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -12980,12 +12972,12 @@
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>VMSB-O-202410001</t>
+          <t>VMSB-O-202410001-N</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同 （WONG CHAI NI）Kelly</t>
+          <t>艺人解除协议（双语）Wong Chai Ni</t>
         </is>
       </c>
       <c r="F149" s="10" t="inlineStr">
@@ -12998,13 +12990,13 @@
           <t>归档</t>
         </is>
       </c>
-      <c r="H149" s="10" t="inlineStr"/>
-      <c r="I149" s="10" t="inlineStr"/>
+      <c r="H149" s="10" t="n"/>
+      <c r="I149" s="10" t="n"/>
       <c r="J149" s="10" t="inlineStr"/>
       <c r="K149" s="11" t="inlineStr"/>
       <c r="L149" s="10" t="inlineStr">
         <is>
-          <t>YU JING YI</t>
+          <t>Thong Wen Yee</t>
         </is>
       </c>
       <c r="M149" s="10" t="inlineStr">
@@ -13056,51 +13048,51 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>VMSB-O-202410001-N</t>
+          <t>VMSB-O-202511001</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>艺人解除协议（双语）Wong Chai Ni</t>
+          <t>独家经纪合同（Chan Jia wen）Cheesy</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-09-08</t>
         </is>
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
-        </is>
-      </c>
-      <c r="H150" s="8" t="n"/>
-      <c r="I150" s="8" t="n"/>
+          <t>用印</t>
+        </is>
+      </c>
+      <c r="H150" s="8" t="inlineStr"/>
+      <c r="I150" s="8" t="inlineStr"/>
       <c r="J150" s="8" t="inlineStr"/>
       <c r="K150" s="9" t="inlineStr"/>
       <c r="L150" s="8" t="inlineStr">
         <is>
-          <t>Thong Wen Yee</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="M150" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N150" s="8" t="inlineStr">
         <is>
-          <t>YU JING YI</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="O150" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P150" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="Q150" s="8" t="inlineStr">
@@ -13110,7 +13102,7 @@
       </c>
       <c r="R150" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -13132,22 +13124,22 @@
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>VMSB-O-202511001</t>
+          <t>VMSB-O-202604001</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Chan Jia wen）Cheesy</t>
+          <t>MZ9M 33 独家经纪约（三三）</t>
         </is>
       </c>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>2027-09-08</t>
+          <t>2028-03-17</t>
         </is>
       </c>
       <c r="G151" s="10" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>上传电子档</t>
         </is>
       </c>
       <c r="H151" s="10" t="inlineStr"/>
@@ -13208,31 +13200,39 @@
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>VMSB-O-202604001</t>
+          <t>XF-B-202401001</t>
         </is>
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>MZ9M 33 独家经纪约（三三）</t>
+          <t>抖音-游戏-剑纯【沈舒晗】独家经纪约-三年</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr">
         <is>
-          <t>2028-03-17</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>上传电子档</t>
-        </is>
-      </c>
-      <c r="H152" s="8" t="inlineStr"/>
-      <c r="I152" s="8" t="inlineStr"/>
+          <t>归档</t>
+        </is>
+      </c>
+      <c r="H152" s="8" t="inlineStr">
+        <is>
+          <t>27559</t>
+        </is>
+      </c>
+      <c r="I152" s="8" t="inlineStr">
+        <is>
+          <t>27559</t>
+        </is>
+      </c>
       <c r="J152" s="8" t="inlineStr"/>
       <c r="K152" s="9" t="inlineStr"/>
       <c r="L152" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>区景桉</t>
         </is>
       </c>
       <c r="M152" s="8" t="inlineStr">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="N152" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>区景桉</t>
         </is>
       </c>
       <c r="O152" s="8" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="P152" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>区景桉</t>
         </is>
       </c>
       <c r="Q152" s="8" t="inlineStr">
@@ -13284,17 +13284,17 @@
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202401001</t>
+          <t>XF-B-202401006</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>抖音-游戏-剑纯【沈舒晗】独家经纪约-三年</t>
+          <t>独家经纪合同-西伐-叶芳盏_霜霜_经纪约-20240110</t>
         </is>
       </c>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G153" s="10" t="inlineStr">
@@ -13304,12 +13304,12 @@
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>27559</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
         <is>
-          <t>27559</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="J153" s="10" t="inlineStr"/>
@@ -13368,17 +13368,17 @@
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202401006</t>
+          <t>XF-B-202401008</t>
         </is>
       </c>
       <c r="E154" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-西伐-叶芳盏_霜霜_经纪约-20240110</t>
+          <t>抖音-王者-闪光独家经纪合同【抖音】</t>
         </is>
       </c>
       <c r="F154" s="8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="G154" s="8" t="inlineStr">
@@ -13388,19 +13388,19 @@
       </c>
       <c r="H154" s="8" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="J154" s="8" t="inlineStr"/>
       <c r="K154" s="9" t="inlineStr"/>
       <c r="L154" s="8" t="inlineStr">
         <is>
-          <t>区景桉</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="M154" s="8" t="inlineStr">
@@ -13410,17 +13410,17 @@
       </c>
       <c r="N154" s="8" t="inlineStr">
         <is>
-          <t>区景桉</t>
+          <t>陈尧</t>
         </is>
       </c>
       <c r="O154" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P154" s="8" t="inlineStr">
         <is>
-          <t>区景桉</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="Q154" s="8" t="inlineStr">
@@ -13452,17 +13452,17 @@
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202401008</t>
+          <t>XF-B-202401009</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>抖音-王者-闪光独家经纪合同【抖音】</t>
+          <t>抖音-游戏-筱七商务&amp;自媒体独家经纪合同</t>
         </is>
       </c>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G155" s="10" t="inlineStr">
@@ -13472,12 +13472,12 @@
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>27842</t>
+          <t>28082</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
-          <t>27842</t>
+          <t>28082</t>
         </is>
       </c>
       <c r="J155" s="10" t="inlineStr"/>
@@ -13494,12 +13494,12 @@
       </c>
       <c r="N155" s="10" t="inlineStr">
         <is>
-          <t>陈尧</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="O155" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P155" s="10" t="inlineStr">
@@ -13536,12 +13536,12 @@
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202401009</t>
+          <t>XF-B-202401009-N</t>
         </is>
       </c>
       <c r="E156" s="9" t="inlineStr">
         <is>
-          <t>抖音-游戏-筱七商务&amp;自媒体独家经纪合同</t>
+          <t>抖音-游戏-筱七独家经纪解除协议</t>
         </is>
       </c>
       <c r="F156" s="8" t="inlineStr">
@@ -13620,32 +13620,32 @@
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202401009-N</t>
+          <t>XF-B-202403001</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>抖音-游戏-筱七独家经纪解除协议</t>
+          <t>抖音-游戏-余生一个小浪浪独家经纪协议</t>
         </is>
       </c>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G157" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>28082</t>
+          <t>28254</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
         <is>
-          <t>28082</t>
+          <t>28254</t>
         </is>
       </c>
       <c r="J157" s="10" t="inlineStr"/>
@@ -13704,32 +13704,32 @@
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202403001</t>
+          <t>XF-B-202404003</t>
         </is>
       </c>
       <c r="E158" s="9" t="inlineStr">
         <is>
-          <t>抖音-游戏-余生一个小浪浪独家经纪协议</t>
+          <t>抖音-游戏-真真酱独家经纪合同</t>
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H158" s="8" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>28354</t>
         </is>
       </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>28354</t>
         </is>
       </c>
       <c r="J158" s="8" t="inlineStr"/>
@@ -13788,12 +13788,12 @@
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202404003</t>
+          <t>XF-B-202404003-N</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>抖音-游戏-真真酱独家经纪合同</t>
+          <t>抖音-游戏-真真经纪解除协议</t>
         </is>
       </c>
       <c r="F159" s="10" t="inlineStr">
@@ -13872,17 +13872,17 @@
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202404003-N</t>
+          <t>XF-B-202404003-S1</t>
         </is>
       </c>
       <c r="E160" s="9" t="inlineStr">
         <is>
-          <t>抖音-游戏-真真经纪解除协议</t>
+          <t>抖音-游戏-真真酱独家经纪补充协议之一</t>
         </is>
       </c>
       <c r="F160" s="8" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G160" s="8" t="inlineStr">
@@ -13956,17 +13956,17 @@
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202404003-S1</t>
+          <t>XF-B-202404005</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>抖音-游戏-真真酱独家经纪补充协议之一</t>
+          <t>抖音-游戏-芝芝经纪协议</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G161" s="10" t="inlineStr">
@@ -13976,12 +13976,12 @@
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="J161" s="10" t="inlineStr"/>
@@ -14040,12 +14040,12 @@
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202404005</t>
+          <t>XF-B-202404005-N</t>
         </is>
       </c>
       <c r="E162" s="9" t="inlineStr">
         <is>
-          <t>抖音-游戏-芝芝经纪协议</t>
+          <t>抖音-游戏-芝芝经纪解除协议</t>
         </is>
       </c>
       <c r="F162" s="8" t="inlineStr">
@@ -14124,17 +14124,17 @@
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202404005-N</t>
+          <t>XF-B-202404007</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>抖音-游戏-芝芝经纪解除协议</t>
+          <t>抖音-游戏-陈楚云独家经纪合同</t>
         </is>
       </c>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G163" s="10" t="inlineStr">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="J163" s="10" t="inlineStr"/>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202404007</t>
+          <t>XF-B-202404007-N</t>
         </is>
       </c>
       <c r="E164" s="9" t="inlineStr">
         <is>
-          <t>抖音-游戏-陈楚云独家经纪合同</t>
+          <t>抖音-游戏-陈楚云解除协议</t>
         </is>
       </c>
       <c r="F164" s="8" t="inlineStr">
@@ -14292,39 +14292,39 @@
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202404007-N</t>
+          <t>XF-B-202412001</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>抖音-游戏-陈楚云解除协议</t>
+          <t>西伐-逐浪抖音-李尚-王者-20241101</t>
         </is>
       </c>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="G165" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H165" s="10" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="J165" s="10" t="inlineStr"/>
       <c r="K165" s="11" t="inlineStr"/>
       <c r="L165" s="10" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>何嘉伟</t>
         </is>
       </c>
       <c r="M165" s="10" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="N165" s="10" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>何嘉伟</t>
         </is>
       </c>
       <c r="O165" s="10" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="P165" s="10" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>何嘉伟</t>
         </is>
       </c>
       <c r="Q165" s="10" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202412001</t>
+          <t>XF-B-202412001-N</t>
         </is>
       </c>
       <c r="E166" s="9" t="inlineStr">
         <is>
-          <t>西伐-逐浪抖音-李尚-王者-20241101</t>
+          <t>抖音-游戏-李尚经纪解除协议</t>
         </is>
       </c>
       <c r="F166" s="8" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H166" s="8" t="inlineStr">
@@ -14408,19 +14408,19 @@
       <c r="K166" s="9" t="inlineStr"/>
       <c r="L166" s="8" t="inlineStr">
         <is>
+          <t>黎小飞</t>
+        </is>
+      </c>
+      <c r="M166" s="8" t="inlineStr">
+        <is>
+          <t>在职</t>
+        </is>
+      </c>
+      <c r="N166" s="8" t="inlineStr">
+        <is>
           <t>何嘉伟</t>
         </is>
       </c>
-      <c r="M166" s="8" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
-      <c r="N166" s="8" t="inlineStr">
-        <is>
-          <t>何嘉伟</t>
-        </is>
-      </c>
       <c r="O166" s="8" t="inlineStr">
         <is>
           <t>在职</t>
@@ -14428,7 +14428,7 @@
       </c>
       <c r="P166" s="8" t="inlineStr">
         <is>
-          <t>何嘉伟</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="Q166" s="8" t="inlineStr">
@@ -14460,17 +14460,17 @@
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202412001-N</t>
+          <t>XF-J-202401001</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>抖音-游戏-李尚经纪解除协议</t>
+          <t>游戏-抖音-西伐&amp;武汉弈极联合运营合同</t>
         </is>
       </c>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="G167" s="10" t="inlineStr">
@@ -14480,12 +14480,12 @@
       </c>
       <c r="H167" s="10" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>27565</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>27565</t>
         </is>
       </c>
       <c r="J167" s="10" t="inlineStr"/>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="N167" s="10" t="inlineStr">
         <is>
-          <t>何嘉伟</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="O167" s="10" t="inlineStr">
@@ -14544,17 +14544,17 @@
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>XF-J-202401001</t>
+          <t>XJ-B-202205001</t>
         </is>
       </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
-          <t>游戏-抖音-西伐&amp;武汉弈极联合运营合同</t>
+          <t>独家经纪合同-赵豪（解说嘉豪）</t>
         </is>
       </c>
       <c r="F168" s="8" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-05-14</t>
         </is>
       </c>
       <c r="G168" s="8" t="inlineStr">
@@ -14564,39 +14564,39 @@
       </c>
       <c r="H168" s="8" t="inlineStr">
         <is>
-          <t>27565</t>
+          <t>19801</t>
         </is>
       </c>
       <c r="I168" s="8" t="inlineStr">
         <is>
-          <t>27565</t>
+          <t>19801</t>
         </is>
       </c>
       <c r="J168" s="8" t="inlineStr"/>
       <c r="K168" s="9" t="inlineStr"/>
       <c r="L168" s="8" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>叶睿</t>
         </is>
       </c>
       <c r="M168" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N168" s="8" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>叶睿</t>
         </is>
       </c>
       <c r="O168" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P168" s="8" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q168" s="8" t="inlineStr">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="R168" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -14628,17 +14628,17 @@
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202205001</t>
+          <t>XJ-B-202206002</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-赵豪（解说嘉豪）</t>
+          <t>独家经纪合同-叶骏成</t>
         </is>
       </c>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>2027-05-14</t>
+          <t>2027-06-26</t>
         </is>
       </c>
       <c r="G169" s="10" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="H169" s="10" t="inlineStr">
         <is>
-          <t>19801</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="I169" s="10" t="inlineStr">
         <is>
-          <t>19801</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="J169" s="10" t="inlineStr"/>
@@ -14712,12 +14712,12 @@
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202206002</t>
+          <t>XJ-B-202206002-N</t>
         </is>
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-叶骏成</t>
+          <t>【香蕉】艺人经纪约解约协议（解说叶骏成）</t>
         </is>
       </c>
       <c r="F170" s="8" t="inlineStr">
@@ -14744,7 +14744,7 @@
       <c r="K170" s="9" t="inlineStr"/>
       <c r="L170" s="8" t="inlineStr">
         <is>
-          <t>叶睿</t>
+          <t>金佳冬</t>
         </is>
       </c>
       <c r="M170" s="8" t="inlineStr">
@@ -14796,17 +14796,17 @@
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202206002-N</t>
+          <t>XJ-B-202206003</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>【香蕉】艺人经纪约解约协议（解说叶骏成）</t>
+          <t>独家经纪合同-吴均远（解说均远）</t>
         </is>
       </c>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>2027-06-26</t>
+          <t>2027-05-31</t>
         </is>
       </c>
       <c r="G171" s="10" t="inlineStr">
@@ -14816,19 +14816,19 @@
       </c>
       <c r="H171" s="10" t="inlineStr">
         <is>
-          <t>21680</t>
+          <t>21738</t>
         </is>
       </c>
       <c r="I171" s="10" t="inlineStr">
         <is>
-          <t>21680</t>
+          <t>21738</t>
         </is>
       </c>
       <c r="J171" s="10" t="inlineStr"/>
       <c r="K171" s="11" t="inlineStr"/>
       <c r="L171" s="10" t="inlineStr">
         <is>
-          <t>金佳冬</t>
+          <t>叶睿</t>
         </is>
       </c>
       <c r="M171" s="10" t="inlineStr">
@@ -14880,12 +14880,12 @@
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202206003</t>
+          <t>XJ-B-202206003-S1</t>
         </is>
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-吴均远（解说均远）</t>
+          <t>独家经纪合同-吴均远-补充协议</t>
         </is>
       </c>
       <c r="F172" s="8" t="inlineStr">
@@ -14912,7 +14912,7 @@
       <c r="K172" s="9" t="inlineStr"/>
       <c r="L172" s="8" t="inlineStr">
         <is>
-          <t>叶睿</t>
+          <t>彭星月</t>
         </is>
       </c>
       <c r="M172" s="8" t="inlineStr">
@@ -14922,7 +14922,7 @@
       </c>
       <c r="N172" s="8" t="inlineStr">
         <is>
-          <t>叶睿</t>
+          <t>彭星月</t>
         </is>
       </c>
       <c r="O172" s="8" t="inlineStr">
@@ -14964,17 +14964,17 @@
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202206003-S1</t>
+          <t>XJ-B-202302003</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-吴均远-补充协议</t>
+          <t>独家经纪合同（覃尚）</t>
         </is>
       </c>
       <c r="F173" s="10" t="inlineStr">
         <is>
-          <t>2027-05-31</t>
+          <t>2028-02-28</t>
         </is>
       </c>
       <c r="G173" s="10" t="inlineStr">
@@ -14984,39 +14984,39 @@
       </c>
       <c r="H173" s="10" t="inlineStr">
         <is>
-          <t>21738</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="I173" s="10" t="inlineStr">
         <is>
-          <t>21738</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="J173" s="10" t="inlineStr"/>
       <c r="K173" s="11" t="inlineStr"/>
       <c r="L173" s="10" t="inlineStr">
         <is>
-          <t>彭星月</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="M173" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N173" s="10" t="inlineStr">
         <is>
-          <t>彭星月</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="O173" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P173" s="10" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="Q173" s="10" t="inlineStr">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="R173" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -15048,17 +15048,17 @@
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202302003</t>
+          <t>XJ-B-202303001</t>
         </is>
       </c>
       <c r="E174" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（覃尚）</t>
+          <t>郭妃妤独家经纪合同</t>
         </is>
       </c>
       <c r="F174" s="8" t="inlineStr">
         <is>
-          <t>2028-02-28</t>
+          <t>2028-03-31</t>
         </is>
       </c>
       <c r="G174" s="8" t="inlineStr">
@@ -15068,12 +15068,12 @@
       </c>
       <c r="H174" s="8" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="I174" s="8" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="J174" s="8" t="inlineStr"/>
@@ -15132,17 +15132,17 @@
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202303001</t>
+          <t>XJ-B-202303002</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
         <is>
-          <t>郭妃妤独家经纪合同</t>
+          <t>独家经纪合同-神乐</t>
         </is>
       </c>
       <c r="F175" s="10" t="inlineStr">
         <is>
-          <t>2028-03-31</t>
+          <t>2028-03-22</t>
         </is>
       </c>
       <c r="G175" s="10" t="inlineStr">
@@ -15152,39 +15152,39 @@
       </c>
       <c r="H175" s="10" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>24429</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>24429</t>
         </is>
       </c>
       <c r="J175" s="10" t="inlineStr"/>
       <c r="K175" s="11" t="inlineStr"/>
       <c r="L175" s="10" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>彭星月</t>
         </is>
       </c>
       <c r="M175" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N175" s="10" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>彭星月</t>
         </is>
       </c>
       <c r="O175" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P175" s="10" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q175" s="10" t="inlineStr">
@@ -15194,7 +15194,7 @@
       </c>
       <c r="R175" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -15216,17 +15216,17 @@
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202303002</t>
+          <t>XJ-B-202306001</t>
         </is>
       </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-神乐</t>
+          <t>独家经纪合同--七之宝</t>
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr">
         <is>
-          <t>2028-03-22</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G176" s="8" t="inlineStr">
@@ -15236,12 +15236,12 @@
       </c>
       <c r="H176" s="8" t="inlineStr">
         <is>
-          <t>24429</t>
+          <t>24891</t>
         </is>
       </c>
       <c r="I176" s="8" t="inlineStr">
         <is>
-          <t>24429</t>
+          <t>24891</t>
         </is>
       </c>
       <c r="J176" s="8" t="inlineStr"/>
@@ -15300,17 +15300,17 @@
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202306001</t>
+          <t>XJ-B-202306003</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同--七之宝</t>
+          <t>独家经纪合同-严友浩</t>
         </is>
       </c>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2028-06-20</t>
         </is>
       </c>
       <c r="G177" s="10" t="inlineStr">
@@ -15320,12 +15320,12 @@
       </c>
       <c r="H177" s="10" t="inlineStr">
         <is>
-          <t>24891</t>
+          <t>24948</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr">
         <is>
-          <t>24891</t>
+          <t>24948</t>
         </is>
       </c>
       <c r="J177" s="10" t="inlineStr"/>
@@ -15384,39 +15384,39 @@
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202306003</t>
+          <t>XJ-B-202307001</t>
         </is>
       </c>
       <c r="E178" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-严友浩</t>
+          <t>圈圈独家经纪合同</t>
         </is>
       </c>
       <c r="F178" s="8" t="inlineStr">
         <is>
-          <t>2028-06-20</t>
+          <t>2028-06-30</t>
         </is>
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H178" s="8" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="I178" s="8" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="J178" s="8" t="inlineStr"/>
       <c r="K178" s="9" t="inlineStr"/>
       <c r="L178" s="8" t="inlineStr">
         <is>
-          <t>彭星月</t>
+          <t>蔡译凡</t>
         </is>
       </c>
       <c r="M178" s="8" t="inlineStr">
@@ -15426,17 +15426,17 @@
       </c>
       <c r="N178" s="8" t="inlineStr">
         <is>
-          <t>彭星月</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="O178" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P178" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="Q178" s="8" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="R178" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人离职,更新为合同执行人</t>
         </is>
       </c>
     </row>
@@ -15468,39 +15468,39 @@
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202307001</t>
+          <t>XJ-B-202307003</t>
         </is>
       </c>
       <c r="E179" s="11" t="inlineStr">
         <is>
-          <t>圈圈独家经纪合同</t>
+          <t>Doby_独家经纪合同（通用版）_20230221_V2.3</t>
         </is>
       </c>
       <c r="F179" s="10" t="inlineStr">
         <is>
-          <t>2028-06-30</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G179" s="10" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H179" s="10" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="J179" s="10" t="inlineStr"/>
       <c r="K179" s="11" t="inlineStr"/>
       <c r="L179" s="10" t="inlineStr">
         <is>
-          <t>蔡译凡</t>
+          <t>宋頔斐</t>
         </is>
       </c>
       <c r="M179" s="10" t="inlineStr">
@@ -15510,17 +15510,17 @@
       </c>
       <c r="N179" s="10" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>宋頔斐</t>
         </is>
       </c>
       <c r="O179" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P179" s="10" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q179" s="10" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="R179" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,更新为合同执行人</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -15552,17 +15552,17 @@
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202307003</t>
+          <t>XJ-B-202307004</t>
         </is>
       </c>
       <c r="E180" s="9" t="inlineStr">
         <is>
-          <t>Doby_独家经纪合同（通用版）_20230221_V2.3</t>
+          <t>童童_独家经纪合同（通用版）_20230221_V2.3</t>
         </is>
       </c>
       <c r="F180" s="8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G180" s="8" t="inlineStr">
@@ -15572,12 +15572,12 @@
       </c>
       <c r="H180" s="8" t="inlineStr">
         <is>
-          <t>26537</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="I180" s="8" t="inlineStr">
         <is>
-          <t>26537</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="J180" s="8" t="inlineStr"/>
@@ -15636,12 +15636,12 @@
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202307004</t>
+          <t>XJ-B-202307005</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
         <is>
-          <t>童童_独家经纪合同（通用版）_20230221_V2.3</t>
+          <t>卡凡独家经纪合同</t>
         </is>
       </c>
       <c r="F181" s="10" t="inlineStr">
@@ -15656,19 +15656,19 @@
       </c>
       <c r="H181" s="10" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="I181" s="10" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="J181" s="10" t="inlineStr"/>
       <c r="K181" s="11" t="inlineStr"/>
       <c r="L181" s="10" t="inlineStr">
         <is>
-          <t>宋頔斐</t>
+          <t>蔡译凡</t>
         </is>
       </c>
       <c r="M181" s="10" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="N181" s="10" t="inlineStr">
         <is>
-          <t>宋頔斐</t>
+          <t>蔡译凡</t>
         </is>
       </c>
       <c r="O181" s="10" t="inlineStr">
@@ -15720,17 +15720,17 @@
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202307005</t>
+          <t>XJ-B-202307006</t>
         </is>
       </c>
       <c r="E182" s="9" t="inlineStr">
         <is>
-          <t>卡凡独家经纪合同</t>
+          <t>Yoho_独家经纪合同（通用版）_20230221_V2.3</t>
         </is>
       </c>
       <c r="F182" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2028-07-31</t>
         </is>
       </c>
       <c r="G182" s="8" t="inlineStr">
@@ -15740,19 +15740,19 @@
       </c>
       <c r="H182" s="8" t="inlineStr">
         <is>
-          <t>26557</t>
+          <t>26545</t>
         </is>
       </c>
       <c r="I182" s="8" t="inlineStr">
         <is>
-          <t>26557</t>
+          <t>26545</t>
         </is>
       </c>
       <c r="J182" s="8" t="inlineStr"/>
       <c r="K182" s="9" t="inlineStr"/>
       <c r="L182" s="8" t="inlineStr">
         <is>
-          <t>蔡译凡</t>
+          <t>宋頔斐</t>
         </is>
       </c>
       <c r="M182" s="8" t="inlineStr">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="N182" s="8" t="inlineStr">
         <is>
-          <t>蔡译凡</t>
+          <t>宋頔斐</t>
         </is>
       </c>
       <c r="O182" s="8" t="inlineStr">
@@ -15804,17 +15804,17 @@
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202307006</t>
+          <t>XJ-B-202308001</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
         <is>
-          <t>Yoho_独家经纪合同（通用版）_20230221_V2.3</t>
+          <t>Fly_独家经纪合同（通用版）_20230221_V2.3</t>
         </is>
       </c>
       <c r="F183" s="10" t="inlineStr">
         <is>
-          <t>2028-07-31</t>
+          <t>2028-08-03</t>
         </is>
       </c>
       <c r="G183" s="10" t="inlineStr">
@@ -15824,12 +15824,12 @@
       </c>
       <c r="H183" s="10" t="inlineStr">
         <is>
-          <t>26545</t>
+          <t>26587</t>
         </is>
       </c>
       <c r="I183" s="10" t="inlineStr">
         <is>
-          <t>26545</t>
+          <t>26587</t>
         </is>
       </c>
       <c r="J183" s="10" t="inlineStr"/>
@@ -15888,39 +15888,39 @@
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202308001</t>
+          <t>XJ-B-202308002</t>
         </is>
       </c>
       <c r="E184" s="9" t="inlineStr">
         <is>
-          <t>Fly_独家经纪合同（通用版）_20230221_V2.3</t>
+          <t>VSPO独家经纪合同-张语希</t>
         </is>
       </c>
       <c r="F184" s="8" t="inlineStr">
         <is>
-          <t>2028-08-03</t>
+          <t>2028-09-01</t>
         </is>
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H184" s="8" t="inlineStr">
         <is>
-          <t>26587</t>
+          <t>26769</t>
         </is>
       </c>
       <c r="I184" s="8" t="inlineStr">
         <is>
-          <t>26587</t>
+          <t>26769</t>
         </is>
       </c>
       <c r="J184" s="8" t="inlineStr"/>
       <c r="K184" s="9" t="inlineStr"/>
       <c r="L184" s="8" t="inlineStr">
         <is>
-          <t>宋頔斐</t>
+          <t>徐如珺</t>
         </is>
       </c>
       <c r="M184" s="8" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="N184" s="8" t="inlineStr">
         <is>
-          <t>宋頔斐</t>
+          <t>徐如珺</t>
         </is>
       </c>
       <c r="O184" s="8" t="inlineStr">
@@ -15972,32 +15972,32 @@
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202308002</t>
+          <t>XJ-B-202309002</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
         <is>
-          <t>VSPO独家经纪合同-张语希</t>
+          <t>【香蕉】VSPO独家经纪合同-逗木doumu</t>
         </is>
       </c>
       <c r="F185" s="10" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G185" s="10" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>上传电子档</t>
         </is>
       </c>
       <c r="H185" s="10" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>26813</t>
         </is>
       </c>
       <c r="I185" s="10" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>26813</t>
         </is>
       </c>
       <c r="J185" s="10" t="inlineStr"/>
@@ -16056,39 +16056,39 @@
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202309002</t>
+          <t>XJ-B-202311001</t>
         </is>
       </c>
       <c r="E186" s="9" t="inlineStr">
         <is>
-          <t>【香蕉】VSPO独家经纪合同-逗木doumu</t>
+          <t>《香蕉》徐培博独家经济合同</t>
         </is>
       </c>
       <c r="F186" s="8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2028-06-20</t>
         </is>
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t>上传电子档</t>
+          <t>法务确认</t>
         </is>
       </c>
       <c r="H186" s="8" t="inlineStr">
         <is>
-          <t>26813</t>
+          <t>27115</t>
         </is>
       </c>
       <c r="I186" s="8" t="inlineStr">
         <is>
-          <t>26813</t>
+          <t>27115</t>
         </is>
       </c>
       <c r="J186" s="8" t="inlineStr"/>
       <c r="K186" s="9" t="inlineStr"/>
       <c r="L186" s="8" t="inlineStr">
         <is>
-          <t>徐如珺</t>
+          <t>吴均远</t>
         </is>
       </c>
       <c r="M186" s="8" t="inlineStr">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="N186" s="8" t="inlineStr">
         <is>
-          <t>徐如珺</t>
+          <t>徐如珺1</t>
         </is>
       </c>
       <c r="O186" s="8" t="inlineStr">
@@ -16140,39 +16140,39 @@
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202311001</t>
+          <t>XJ-B-202401001</t>
         </is>
       </c>
       <c r="E187" s="11" t="inlineStr">
         <is>
-          <t>《香蕉》徐培博独家经济合同</t>
+          <t>重越_独家经纪合同（通用版）_20230221_V2.3</t>
         </is>
       </c>
       <c r="F187" s="10" t="inlineStr">
         <is>
-          <t>2028-06-20</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="G187" s="10" t="inlineStr">
         <is>
-          <t>法务确认</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H187" s="10" t="inlineStr">
         <is>
-          <t>27115</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="I187" s="10" t="inlineStr">
         <is>
-          <t>27115</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="J187" s="10" t="inlineStr"/>
       <c r="K187" s="11" t="inlineStr"/>
       <c r="L187" s="10" t="inlineStr">
         <is>
-          <t>吴均远</t>
+          <t>宋頔斐</t>
         </is>
       </c>
       <c r="M187" s="10" t="inlineStr">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="N187" s="10" t="inlineStr">
         <is>
-          <t>徐如珺1</t>
+          <t>宋頔斐</t>
         </is>
       </c>
       <c r="O187" s="10" t="inlineStr">
@@ -16224,17 +16224,17 @@
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202401001</t>
+          <t>XJ-B-202402001</t>
         </is>
       </c>
       <c r="E188" s="9" t="inlineStr">
         <is>
-          <t>重越_独家经纪合同（通用版）_20230221_V2.3</t>
+          <t>王梓源_独家经纪合同（通用版）_20230221_V2.3</t>
         </is>
       </c>
       <c r="F188" s="8" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2029-02-28</t>
         </is>
       </c>
       <c r="G188" s="8" t="inlineStr">
@@ -16244,19 +16244,19 @@
       </c>
       <c r="H188" s="8" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>28224</t>
         </is>
       </c>
       <c r="I188" s="8" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>28224</t>
         </is>
       </c>
       <c r="J188" s="8" t="inlineStr"/>
       <c r="K188" s="9" t="inlineStr"/>
       <c r="L188" s="8" t="inlineStr">
         <is>
-          <t>宋頔斐</t>
+          <t>宋頔斐1</t>
         </is>
       </c>
       <c r="M188" s="8" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="N188" s="8" t="inlineStr">
         <is>
-          <t>宋頔斐</t>
+          <t>宋頔斐1</t>
         </is>
       </c>
       <c r="O188" s="8" t="inlineStr">
@@ -16290,92 +16290,8 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="B189" s="10" t="inlineStr">
-        <is>
-          <t>未发生替换仍未命中Hand</t>
-        </is>
-      </c>
-      <c r="C189" s="10" t="inlineStr">
-        <is>
-          <t>Hand生产库未命中</t>
-        </is>
-      </c>
-      <c r="D189" s="10" t="inlineStr">
-        <is>
-          <t>XJ-B-202402001</t>
-        </is>
-      </c>
-      <c r="E189" s="11" t="inlineStr">
-        <is>
-          <t>王梓源_独家经纪合同（通用版）_20230221_V2.3</t>
-        </is>
-      </c>
-      <c r="F189" s="10" t="inlineStr">
-        <is>
-          <t>2029-02-28</t>
-        </is>
-      </c>
-      <c r="G189" s="10" t="inlineStr">
-        <is>
-          <t>归档</t>
-        </is>
-      </c>
-      <c r="H189" s="10" t="inlineStr">
-        <is>
-          <t>28224</t>
-        </is>
-      </c>
-      <c r="I189" s="10" t="inlineStr">
-        <is>
-          <t>28224</t>
-        </is>
-      </c>
-      <c r="J189" s="10" t="inlineStr"/>
-      <c r="K189" s="11" t="inlineStr"/>
-      <c r="L189" s="10" t="inlineStr">
-        <is>
-          <t>宋頔斐1</t>
-        </is>
-      </c>
-      <c r="M189" s="10" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
-      <c r="N189" s="10" t="inlineStr">
-        <is>
-          <t>宋頔斐1</t>
-        </is>
-      </c>
-      <c r="O189" s="10" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
-      <c r="P189" s="10" t="inlineStr">
-        <is>
-          <t>李家琪</t>
-        </is>
-      </c>
-      <c r="Q189" s="10" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
-      <c r="R189" s="11" t="inlineStr">
-        <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:R189"/>
+  <autoFilter ref="A1:R188"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/contract_anchor_db/Hand主播档案仍未命中_替换后_20260629.xlsx
+++ b/output/contract_anchor_db/Hand主播档案仍未命中_替换后_20260629.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="187条清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="183条清单" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'187条清单'!$A$1:$R$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'183条清单'!$A$1:$R$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8">
@@ -627,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R188"/>
+  <dimension ref="A1:R184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8500,17 +8500,17 @@
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>LZ-B-202408001</t>
+          <t>NP-JS-20210520-S1</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-tiktok- 泡泡（廖丹）</t>
+          <t>NP-JS-20210520-S1-《独家经纪合同》之补充协议（二）-厚翰和金泰相-0-20211203</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -8518,41 +8518,33 @@
           <t>归档</t>
         </is>
       </c>
-      <c r="H95" s="10" t="inlineStr">
-        <is>
-          <t>28996</t>
-        </is>
-      </c>
-      <c r="I95" s="10" t="inlineStr">
-        <is>
-          <t>28996</t>
-        </is>
-      </c>
+      <c r="H95" s="10" t="n"/>
+      <c r="I95" s="10" t="n"/>
       <c r="J95" s="10" t="inlineStr"/>
       <c r="K95" s="11" t="inlineStr"/>
       <c r="L95" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="M95" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N95" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="O95" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P95" s="10" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="Q95" s="10" t="inlineStr">
@@ -8562,7 +8554,7 @@
       </c>
       <c r="R95" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -8584,12 +8576,12 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1</t>
+          <t>NP-JS-20210520-S1-S1</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1-《独家经纪合同》之补充协议（二）-厚翰和金泰相-0-20211203</t>
+          <t>合同主体变更四方协议-厚翰金泰相栗金闪金</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
@@ -8599,7 +8591,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>法务确认</t>
         </is>
       </c>
       <c r="H96" s="8" t="n"/>
@@ -8660,12 +8652,12 @@
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1-S1</t>
+          <t>NP-JS-20210520-S1-S2</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>合同主体变更四方协议-厚翰金泰相栗金闪金</t>
+          <t>补充账户信息-三方协议-Doinb厚翰闪金</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
@@ -8675,7 +8667,7 @@
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>法务确认</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H97" s="10" t="n"/>
@@ -8684,29 +8676,29 @@
       <c r="K97" s="11" t="inlineStr"/>
       <c r="L97" s="10" t="inlineStr">
         <is>
+          <t>梁浩嘉</t>
+        </is>
+      </c>
+      <c r="M97" s="10" t="inlineStr">
+        <is>
+          <t>离职</t>
+        </is>
+      </c>
+      <c r="N97" s="10" t="inlineStr">
+        <is>
           <t>彭敏</t>
         </is>
       </c>
-      <c r="M97" s="10" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
-      <c r="N97" s="10" t="inlineStr">
+      <c r="O97" s="10" t="inlineStr">
+        <is>
+          <t>在职</t>
+        </is>
+      </c>
+      <c r="P97" s="10" t="inlineStr">
         <is>
           <t>彭敏</t>
         </is>
       </c>
-      <c r="O97" s="10" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
-      <c r="P97" s="10" t="inlineStr">
-        <is>
-          <t>彭敏</t>
-        </is>
-      </c>
       <c r="Q97" s="10" t="inlineStr">
         <is>
           <t>在职</t>
@@ -8714,7 +8706,7 @@
       </c>
       <c r="R97" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,更新为合同执行人</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8728,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1-S2</t>
+          <t>NP-JS-20210520-S1-S3</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
@@ -8751,7 +8743,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>法务确认</t>
         </is>
       </c>
       <c r="H98" s="8" t="n"/>
@@ -8760,12 +8752,12 @@
       <c r="K98" s="9" t="inlineStr"/>
       <c r="L98" s="8" t="inlineStr">
         <is>
-          <t>梁浩嘉</t>
+          <t>胡浥盟</t>
         </is>
       </c>
       <c r="M98" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N98" s="8" t="inlineStr">
@@ -8780,7 +8772,7 @@
       </c>
       <c r="P98" s="8" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>胡浥盟</t>
         </is>
       </c>
       <c r="Q98" s="8" t="inlineStr">
@@ -8790,7 +8782,7 @@
       </c>
       <c r="R98" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,更新为合同执行人</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8804,12 @@
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1-S3</t>
+          <t>NP-JS-20210520-S1-S4</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>补充账户信息-三方协议-Doinb厚翰闪金</t>
+          <t>合同主体变更四方协议-厚翰金泰相闪金浅擎</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
@@ -8836,7 +8828,7 @@
       <c r="K99" s="11" t="inlineStr"/>
       <c r="L99" s="10" t="inlineStr">
         <is>
-          <t>胡浥盟</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="M99" s="10" t="inlineStr">
@@ -8856,7 +8848,7 @@
       </c>
       <c r="P99" s="10" t="inlineStr">
         <is>
-          <t>胡浥盟</t>
+          <t>彭敏</t>
         </is>
       </c>
       <c r="Q99" s="10" t="inlineStr">
@@ -8888,12 +8880,12 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1-S4</t>
+          <t>NP-JS-20210520-S1-S5</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>合同主体变更四方协议-厚翰金泰相闪金浅擎</t>
+          <t>斗鱼直播一部游戏组-金泰相-《独家经纪合同》之补充协议（三）（主播昵称：金咕咕金咕咕doinb ）(主播姓名：金泰相 )</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
@@ -8903,7 +8895,7 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>法务确认</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H100" s="8" t="n"/>
@@ -8964,22 +8956,22 @@
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>NP-JS-20210520-S1-S5</t>
+          <t>NP-JS-202107-N</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>斗鱼直播一部游戏组-金泰相-《独家经纪合同》之补充协议（三）（主播昵称：金咕咕金咕咕doinb ）(主播姓名：金泰相 )</t>
+          <t>厚翰—主播姚琳解约协议</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H101" s="10" t="n"/>
@@ -8988,27 +8980,27 @@
       <c r="K101" s="11" t="inlineStr"/>
       <c r="L101" s="10" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>黄芷萱</t>
         </is>
       </c>
       <c r="M101" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N101" s="10" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>周玉婷</t>
         </is>
       </c>
       <c r="O101" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P101" s="10" t="inlineStr">
         <is>
-          <t>彭敏</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q101" s="10" t="inlineStr">
@@ -9018,7 +9010,7 @@
       </c>
       <c r="R101" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -9040,17 +9032,17 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>NP-JS-202107-N</t>
+          <t>QS-B-202306001</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>厚翰—主播姚琳解约协议</t>
+          <t>抖音娱乐主播-于格格（鱼鱼）独家经纪约</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
@@ -9058,33 +9050,41 @@
           <t>归档</t>
         </is>
       </c>
-      <c r="H102" s="8" t="n"/>
-      <c r="I102" s="8" t="n"/>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>24887</t>
+        </is>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>24887</t>
+        </is>
+      </c>
       <c r="J102" s="8" t="inlineStr"/>
       <c r="K102" s="9" t="inlineStr"/>
       <c r="L102" s="8" t="inlineStr">
         <is>
-          <t>黄芷萱</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N102" s="8" t="inlineStr">
         <is>
-          <t>周玉婷</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="O102" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P102" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="Q102" s="8" t="inlineStr">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="R102" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -9116,59 +9116,59 @@
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>QS-B-202306001</t>
+          <t>QS-B-202308028</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>抖音娱乐主播-于格格（鱼鱼）独家经纪约</t>
+          <t>【擎狮合同】米米主播经纪合同</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>法务确认</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>26788</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>26788</t>
         </is>
       </c>
       <c r="J103" s="10" t="inlineStr"/>
       <c r="K103" s="11" t="inlineStr"/>
       <c r="L103" s="10" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>张靖</t>
         </is>
       </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N103" s="10" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>张靖</t>
         </is>
       </c>
       <c r="O103" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P103" s="10" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q103" s="10" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="R103" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -9200,17 +9200,17 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>QS-B-202308028</t>
+          <t>QS-O-202307001</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>【擎狮合同】米米主播经纪合同</t>
+          <t>渠道经纪合作协议-苏杰</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
@@ -9220,39 +9220,39 @@
       </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>26788</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>26788</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr"/>
       <c r="K104" s="9" t="inlineStr"/>
       <c r="L104" s="8" t="inlineStr">
         <is>
-          <t>张靖</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N104" s="8" t="inlineStr">
         <is>
-          <t>张靖</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="O104" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P104" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>鲁冬阳</t>
         </is>
       </c>
       <c r="Q104" s="8" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="R104" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>QS-O-202307001</t>
+          <t>QS-O-202310001</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>法务确认</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
@@ -9368,17 +9368,17 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>QS-O-202310001</t>
+          <t>SHSY-B-202404003</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>渠道经纪合作协议-苏杰</t>
+          <t>独家经纪合同-tiktok- 小奕（王秋涵）</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2027-04-11</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr">
@@ -9388,39 +9388,39 @@
       </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>28355</t>
         </is>
       </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>28355</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr"/>
       <c r="K106" s="9" t="inlineStr"/>
       <c r="L106" s="8" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="M106" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N106" s="8" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="O106" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P106" s="8" t="inlineStr">
         <is>
-          <t>鲁冬阳</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q106" s="8" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="R106" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -9452,17 +9452,17 @@
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202404003</t>
+          <t>SHSY-B-202404004</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-tiktok- 小奕（王秋涵）</t>
+          <t>独家经纪合同-tiktok-ka ka（旦真泽郎）</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>2027-04-11</t>
+          <t>2027-04-02</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>28355</t>
+          <t>28345</t>
         </is>
       </c>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>28355</t>
+          <t>28345</t>
         </is>
       </c>
       <c r="J107" s="10" t="inlineStr"/>
@@ -9536,17 +9536,17 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202404004</t>
+          <t>SHSY-B-202407002</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-tiktok-ka ka（旦真泽郎）</t>
+          <t>主播经纪合同-tiktok-（黄志伟）</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>2027-04-02</t>
+          <t>2027-06-30</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr"/>
@@ -9620,17 +9620,17 @@
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202407002</t>
+          <t>SHSY-B-202407003</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>主播经纪合同-tiktok-（黄志伟）</t>
+          <t>独家经纪合同-tiktok- 邓雅兰（小九）</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>2027-06-30</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
@@ -9640,19 +9640,19 @@
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>28881</t>
+          <t>28924</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr">
         <is>
-          <t>28881</t>
+          <t>28924</t>
         </is>
       </c>
       <c r="J109" s="10" t="inlineStr"/>
       <c r="K109" s="11" t="inlineStr"/>
       <c r="L109" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>路钰忠</t>
         </is>
       </c>
       <c r="M109" s="10" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="N109" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>路钰忠</t>
         </is>
       </c>
       <c r="O109" s="10" t="inlineStr">
@@ -9704,39 +9704,39 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202407003</t>
+          <t>SHSY-B-202408003</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-tiktok- 邓雅兰（小九）</t>
+          <t>独家经纪协议-抖音-李金阳</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2027-08-14</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>28924</t>
+          <t>28992</t>
         </is>
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>28924</t>
+          <t>28992</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr"/>
       <c r="K110" s="9" t="inlineStr"/>
       <c r="L110" s="8" t="inlineStr">
         <is>
-          <t>路钰忠</t>
+          <t>宋进</t>
         </is>
       </c>
       <c r="M110" s="8" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="N110" s="8" t="inlineStr">
         <is>
-          <t>路钰忠</t>
+          <t>宋进</t>
         </is>
       </c>
       <c r="O110" s="8" t="inlineStr">
@@ -9788,39 +9788,39 @@
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202407004</t>
+          <t>SHSY-B-202408003-N</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>主播经纪合同-tiktok-（吕思盟）</t>
+          <t>解除协议-抖音-李金阳</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2027-08-14</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>28992</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>28992</t>
         </is>
       </c>
       <c r="J111" s="10" t="inlineStr"/>
       <c r="K111" s="11" t="inlineStr"/>
       <c r="L111" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>乔颖</t>
         </is>
       </c>
       <c r="M111" s="10" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="N111" s="10" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>宋进</t>
         </is>
       </c>
       <c r="O111" s="10" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202408003</t>
+          <t>SHSY-B-202408004</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-李金阳</t>
+          <t>独家经纪协议-抖音-曾一凡</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
@@ -9887,17 +9887,17 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>28992</t>
+          <t>28994</t>
         </is>
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>28992</t>
+          <t>28994</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr"/>
@@ -9956,12 +9956,12 @@
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202408003-N</t>
+          <t>SHSY-B-202408004-N</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>解除协议-抖音-李金阳</t>
+          <t>解除协议-抖音-曾一凡</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>28992</t>
+          <t>28994</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
         <is>
-          <t>28992</t>
+          <t>28994</t>
         </is>
       </c>
       <c r="J113" s="10" t="inlineStr"/>
@@ -10040,39 +10040,39 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202408004</t>
+          <t>SHSY-B-202408006</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-曾一凡</t>
+          <t>独家经纪合同-tiktok- 泡泡（廖丹）</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
-          <t>2027-08-14</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>上传电子档</t>
         </is>
       </c>
       <c r="H114" s="8" t="inlineStr">
         <is>
-          <t>28994</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>28994</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr"/>
       <c r="K114" s="9" t="inlineStr"/>
       <c r="L114" s="8" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="M114" s="8" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="N114" s="8" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>刘天桥</t>
         </is>
       </c>
       <c r="O114" s="8" t="inlineStr">
@@ -10124,39 +10124,39 @@
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202408004-N</t>
+          <t>SHSY-B-202408016</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>解除协议-抖音-曾一凡</t>
+          <t>独家经纪协议-抖音-胥梦娇</t>
         </is>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>2027-08-14</t>
+          <t>2027-08-26</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>28994</t>
+          <t>29116</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr">
         <is>
-          <t>28994</t>
+          <t>29116</t>
         </is>
       </c>
       <c r="J115" s="10" t="inlineStr"/>
       <c r="K115" s="11" t="inlineStr"/>
       <c r="L115" s="10" t="inlineStr">
         <is>
-          <t>乔颖</t>
+          <t>宋进</t>
         </is>
       </c>
       <c r="M115" s="10" t="inlineStr">
@@ -10208,39 +10208,39 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202408006</t>
+          <t>SHSY-B-202409002</t>
         </is>
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-tiktok- 泡泡（廖丹）</t>
+          <t>独家经纪协议-抖音-颜亚欣</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2027-08-29</t>
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>上传电子档</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
         <is>
-          <t>28996</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>28996</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr"/>
       <c r="K116" s="9" t="inlineStr"/>
       <c r="L116" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>宋进</t>
         </is>
       </c>
       <c r="M116" s="8" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="N116" s="8" t="inlineStr">
         <is>
-          <t>刘天桥</t>
+          <t>宋进</t>
         </is>
       </c>
       <c r="O116" s="8" t="inlineStr">
@@ -10292,39 +10292,39 @@
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202408016</t>
+          <t>SHSY-B-202409005</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-胥梦娇</t>
+          <t>主播经纪合同-tiktok-（吕思盟）</t>
         </is>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>2027-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>29116</t>
+          <t>28925</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr">
         <is>
-          <t>29116</t>
+          <t>28925</t>
         </is>
       </c>
       <c r="J117" s="10" t="inlineStr"/>
       <c r="K117" s="11" t="inlineStr"/>
       <c r="L117" s="10" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>路钰忠</t>
         </is>
       </c>
       <c r="M117" s="10" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="N117" s="10" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>路钰忠</t>
         </is>
       </c>
       <c r="O117" s="10" t="inlineStr">
@@ -10376,39 +10376,39 @@
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202408019</t>
+          <t>SHSY-B-202409009</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>独家经济协议-抖音-颜亚欣</t>
+          <t>独家经纪协议-抖音-王瑶</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
-          <t>2027-09-14</t>
+          <t>2027-09-26</t>
         </is>
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>上传电子档</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>29147</t>
+          <t>29223</t>
         </is>
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>29147</t>
+          <t>29223</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr"/>
       <c r="K118" s="9" t="inlineStr"/>
       <c r="L118" s="8" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>乔颖</t>
         </is>
       </c>
       <c r="M118" s="8" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="N118" s="8" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>乔颖</t>
         </is>
       </c>
       <c r="O118" s="8" t="inlineStr">
@@ -10460,39 +10460,39 @@
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202409002</t>
+          <t>SHSY-B-202410003</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-颜亚欣</t>
+          <t>独家经纪协议-抖音-钟佳芮</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>2027-08-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>上传电子档</t>
         </is>
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>29147</t>
+          <t>29354</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
         <is>
-          <t>29147</t>
+          <t>29354</t>
         </is>
       </c>
       <c r="J119" s="10" t="inlineStr"/>
       <c r="K119" s="11" t="inlineStr"/>
       <c r="L119" s="10" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>乔颖</t>
         </is>
       </c>
       <c r="M119" s="10" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="N119" s="10" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>乔颖</t>
         </is>
       </c>
       <c r="O119" s="10" t="inlineStr">
@@ -10544,17 +10544,17 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202409003</t>
+          <t>VMSB-B-202501002</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-赵丹</t>
+          <t>独家经纪合同（En En）</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
-          <t>2027-09-10</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G120" s="8" t="inlineStr">
@@ -10564,39 +10564,39 @@
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>29174</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>29174</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr"/>
       <c r="K120" s="9" t="inlineStr"/>
       <c r="L120" s="8" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>Wei Shi (Jessy) Chang</t>
         </is>
       </c>
       <c r="M120" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N120" s="8" t="inlineStr">
         <is>
-          <t>宋进</t>
+          <t>Wei Shi (Jessy) Chang</t>
         </is>
       </c>
       <c r="O120" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P120" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>Wei Shi (Jessy) Chang</t>
         </is>
       </c>
       <c r="Q120" s="8" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="R120" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -10628,59 +10628,59 @@
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202409005</t>
+          <t>VMSB-B-202501002-N</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>主播经纪合同-tiktok-（吕思盟）</t>
+          <t>艺人解除协议（双语）Tan Ru Enn</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="J121" s="10" t="inlineStr"/>
       <c r="K121" s="11" t="inlineStr"/>
       <c r="L121" s="10" t="inlineStr">
         <is>
-          <t>路钰忠</t>
+          <t>Wei Shi (Jessy) Chang</t>
         </is>
       </c>
       <c r="M121" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N121" s="10" t="inlineStr">
         <is>
-          <t>路钰忠</t>
+          <t>Wei Shi (Jessy) Chang</t>
         </is>
       </c>
       <c r="O121" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P121" s="10" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>Wei Shi (Jessy) Chang</t>
         </is>
       </c>
       <c r="Q121" s="10" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="R121" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -10712,59 +10712,59 @@
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>SHSY-B-202409009</t>
+          <t>VMSB-B-202504003</t>
         </is>
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-王瑶</t>
+          <t>独家经纪合同（Chia Qi Er）</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr">
         <is>
-          <t>2027-09-26</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>上传电子档</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>29216</t>
         </is>
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>29216</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr"/>
       <c r="K122" s="9" t="inlineStr"/>
       <c r="L122" s="8" t="inlineStr">
         <is>
-          <t>乔颖</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="M122" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N122" s="8" t="inlineStr">
         <is>
-          <t>乔颖</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="O122" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P122" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="Q122" s="8" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="R122" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -10796,59 +10796,59 @@
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>SHSY-B-202410003</t>
+          <t>VMSB-B-202504004</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>独家经纪协议-抖音-钟佳芮</t>
+          <t>独家经纪合同（Ngoi Suen Jia）</t>
         </is>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
         <is>
-          <t>上传电子档</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>29354</t>
+          <t>29385</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>29354</t>
+          <t>29385</t>
         </is>
       </c>
       <c r="J123" s="10" t="inlineStr"/>
       <c r="K123" s="11" t="inlineStr"/>
       <c r="L123" s="10" t="inlineStr">
         <is>
-          <t>乔颖</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="M123" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N123" s="10" t="inlineStr">
         <is>
-          <t>乔颖</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="O123" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P123" s="10" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="Q123" s="10" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="R123" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -10880,17 +10880,17 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202501002</t>
+          <t>VMSB-B-202504005</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（En En）</t>
+          <t>独家经纪合同（CHIN ROU JING) Joanne</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2027-06-22</t>
         </is>
       </c>
       <c r="G124" s="8" t="inlineStr">
@@ -10900,19 +10900,19 @@
       </c>
       <c r="H124" s="8" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr"/>
       <c r="K124" s="9" t="inlineStr"/>
       <c r="L124" s="8" t="inlineStr">
         <is>
-          <t>Wei Shi (Jessy) Chang</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="M124" s="8" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="N124" s="8" t="inlineStr">
         <is>
-          <t>Wei Shi (Jessy) Chang</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="O124" s="8" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="P124" s="8" t="inlineStr">
         <is>
-          <t>Wei Shi (Jessy) Chang</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="Q124" s="8" t="inlineStr">
@@ -10964,39 +10964,39 @@
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202501002-N</t>
+          <t>VMSB-B-202504006</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>艺人解除协议（双语）Tan Ru Enn</t>
+          <t>独家经纪合同（CHEONG LEI KENG) Elsa</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2027-04-23</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="J125" s="10" t="inlineStr"/>
       <c r="K125" s="11" t="inlineStr"/>
       <c r="L125" s="10" t="inlineStr">
         <is>
-          <t>Wei Shi (Jessy) Chang</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="M125" s="10" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="N125" s="10" t="inlineStr">
         <is>
-          <t>Wei Shi (Jessy) Chang</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="O125" s="10" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P125" s="10" t="inlineStr">
         <is>
-          <t>Wei Shi (Jessy) Chang</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="Q125" s="10" t="inlineStr">
@@ -11048,17 +11048,17 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202504003</t>
+          <t>VMSB-B-202504008</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Chia Qi Er）</t>
+          <t>独家经纪合同（WENDY CALANDRIA TAN) Emma</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
         <is>
-          <t>2027-03-31</t>
+          <t>2027-04-24</t>
         </is>
       </c>
       <c r="G126" s="8" t="inlineStr">
@@ -11068,19 +11068,19 @@
       </c>
       <c r="H126" s="8" t="inlineStr">
         <is>
-          <t>29216</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>29216</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="J126" s="8" t="inlineStr"/>
       <c r="K126" s="9" t="inlineStr"/>
       <c r="L126" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="M126" s="8" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="N126" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="O126" s="8" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P126" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="Q126" s="8" t="inlineStr">
@@ -11132,17 +11132,17 @@
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202504004</t>
+          <t>VMSB-B-202504009</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Ngoi Suen Jia）</t>
+          <t>独家经纪合同（Chong Shun Yee Vinette）</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>2027-03-31</t>
+          <t>2027-04-13</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>29848</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>29848</t>
         </is>
       </c>
       <c r="J127" s="10" t="inlineStr"/>
@@ -11216,17 +11216,17 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202504005</t>
+          <t>VMSB-B-202504016</t>
         </is>
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（CHIN ROU JING) Joanne</t>
+          <t>独家经纪合同（Candy Chan Jia Tong）</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
         <is>
-          <t>2027-06-22</t>
+          <t>2027-04-20</t>
         </is>
       </c>
       <c r="G128" s="8" t="inlineStr">
@@ -11236,19 +11236,19 @@
       </c>
       <c r="H128" s="8" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>29854</t>
         </is>
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>29854</t>
         </is>
       </c>
       <c r="J128" s="8" t="inlineStr"/>
       <c r="K128" s="9" t="inlineStr"/>
       <c r="L128" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="M128" s="8" t="inlineStr">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="N128" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="O128" s="8" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="P128" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="Q128" s="8" t="inlineStr">
@@ -11300,59 +11300,59 @@
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202504006</t>
+          <t>VMSB-B-202506001</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（CHEONG LEI KENG) Elsa</t>
+          <t>独家经纪合同（Edison）</t>
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>2027-04-23</t>
+          <t>2027-06-10</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>28947</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
         <is>
-          <t>28947</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="J129" s="10" t="inlineStr"/>
       <c r="K129" s="11" t="inlineStr"/>
       <c r="L129" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>Sze Yu Lim</t>
         </is>
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N129" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>Sze Yu Lim</t>
         </is>
       </c>
       <c r="O129" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P129" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q129" s="10" t="inlineStr">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="R129" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -11384,32 +11384,32 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202504008</t>
+          <t>VMSB-B-202508002</t>
         </is>
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（WENDY CALANDRIA TAN) Emma</t>
+          <t>独家经纪合同（Tang Huan Ting）yaya</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
         <is>
-          <t>2027-04-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H130" s="8" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr"/>
@@ -11468,17 +11468,17 @@
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202504009</t>
+          <t>VMSB-B-202508003</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Chong Shun Yee Vinette）</t>
+          <t>独家经纪合同（Lee Hsueh En）Snowie</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>2027-04-13</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
@@ -11488,19 +11488,19 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>29848</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
         <is>
-          <t>29848</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="J131" s="10" t="inlineStr"/>
       <c r="K131" s="11" t="inlineStr"/>
       <c r="L131" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="M131" s="10" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="N131" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="O131" s="10" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="P131" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="Q131" s="10" t="inlineStr">
@@ -11552,17 +11552,17 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202504016</t>
+          <t>VMSB-B-202508004</t>
         </is>
       </c>
       <c r="E132" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Candy Chan Jia Tong）</t>
+          <t>独家经纪合同（Chow Si Wei）Bella</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
         <is>
-          <t>2027-04-20</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G132" s="8" t="inlineStr">
@@ -11572,19 +11572,19 @@
       </c>
       <c r="H132" s="8" t="inlineStr">
         <is>
-          <t>29854</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>29854</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr"/>
       <c r="K132" s="9" t="inlineStr"/>
       <c r="L132" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="M132" s="8" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="N132" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="O132" s="8" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="P132" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="Q132" s="8" t="inlineStr">
@@ -11636,17 +11636,17 @@
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202506001</t>
+          <t>VMSB-B-202509002</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Edison）</t>
+          <t>独家经纪合同（Tang Khye Rine）Cat</t>
         </is>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>2027-06-10</t>
+          <t>2027-08-31</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
@@ -11656,39 +11656,39 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="J133" s="10" t="inlineStr"/>
       <c r="K133" s="11" t="inlineStr"/>
       <c r="L133" s="10" t="inlineStr">
         <is>
-          <t>Sze Yu Lim</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N133" s="10" t="inlineStr">
         <is>
-          <t>Sze Yu Lim</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="O133" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P133" s="10" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="Q133" s="10" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="R133" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -11720,32 +11720,32 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202508002</t>
+          <t>VMSB-B-202509005</t>
         </is>
       </c>
       <c r="E134" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Tang Huan Ting）yaya</t>
+          <t>独家经纪合同 (Chan Jia wen)</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2027-09-08</t>
         </is>
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H134" s="8" t="inlineStr">
         <is>
-          <t>30283</t>
+          <t>30677</t>
         </is>
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>30283</t>
+          <t>30677</t>
         </is>
       </c>
       <c r="J134" s="8" t="inlineStr"/>
@@ -11804,32 +11804,32 @@
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202508003</t>
+          <t>VMSB-B-202510005</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Lee Hsueh En）Snowie</t>
+          <t>主播租赁协议（EMMA）</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="J135" s="10" t="inlineStr"/>
@@ -11888,32 +11888,32 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202508004</t>
+          <t>VMSB-B-202511001</t>
         </is>
       </c>
       <c r="E136" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Chow Si Wei）Bella</t>
+          <t>独家经纪合同（Yaw Mei Yen）Peanuat</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2027-10-31</t>
         </is>
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H136" s="8" t="inlineStr">
         <is>
-          <t>30281</t>
+          <t>30860</t>
         </is>
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
-          <t>30281</t>
+          <t>30860</t>
         </is>
       </c>
       <c r="J136" s="8" t="inlineStr"/>
@@ -11972,17 +11972,17 @@
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202509002</t>
+          <t>VMSB-B-202511002</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Tang Khye Rine）Cat</t>
+          <t>独家经纪合同（Kang Chung Hong- Jden）</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>2027-08-31</t>
+          <t>2027-11-22</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>30514</t>
+          <t>30859</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
         <is>
-          <t>30514</t>
+          <t>30859</t>
         </is>
       </c>
       <c r="J137" s="10" t="inlineStr"/>
@@ -12056,17 +12056,17 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202509005</t>
+          <t>VMSB-B-202511004</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同 (Chan Jia wen)</t>
+          <t>独家经纪合同（Chewy）</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
-          <t>2027-09-08</t>
+          <t>2027-11-09</t>
         </is>
       </c>
       <c r="G138" s="8" t="inlineStr">
@@ -12076,19 +12076,19 @@
       </c>
       <c r="H138" s="8" t="inlineStr">
         <is>
-          <t>30677</t>
+          <t>31032</t>
         </is>
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
-          <t>30677</t>
+          <t>31032</t>
         </is>
       </c>
       <c r="J138" s="8" t="inlineStr"/>
       <c r="K138" s="9" t="inlineStr"/>
       <c r="L138" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="M138" s="8" t="inlineStr">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="N138" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="O138" s="8" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="P138" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="Q138" s="8" t="inlineStr">
@@ -12140,39 +12140,39 @@
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202510005</t>
+          <t>VMSB-B-202511005</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>主播租赁协议（EMMA）</t>
+          <t>独家经纪合同（Nini）</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2027-11-09</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="J139" s="10" t="inlineStr"/>
       <c r="K139" s="11" t="inlineStr"/>
       <c r="L139" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="M139" s="10" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="N139" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="O139" s="10" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="P139" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="Q139" s="10" t="inlineStr">
@@ -12224,39 +12224,39 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202511001</t>
+          <t>VMSB-B-202511006</t>
         </is>
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Yaw Mei Yen）Peanuat</t>
+          <t>独家经纪合同</t>
         </is>
       </c>
       <c r="F140" s="8" t="inlineStr">
         <is>
-          <t>2027-10-31</t>
+          <t>2027-11-09</t>
         </is>
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H140" s="8" t="inlineStr">
         <is>
-          <t>30860</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>30860</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="J140" s="8" t="inlineStr"/>
       <c r="K140" s="9" t="inlineStr"/>
       <c r="L140" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="M140" s="8" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="N140" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="O140" s="8" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="P140" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="Q140" s="8" t="inlineStr">
@@ -12308,17 +12308,17 @@
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202511002</t>
+          <t>VMSB-B-202511007</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Kang Chung Hong- Jden）</t>
+          <t>独家经纪合同（Mika）</t>
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>2027-11-22</t>
+          <t>2027-11-09</t>
         </is>
       </c>
       <c r="G141" s="10" t="inlineStr">
@@ -12328,19 +12328,19 @@
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>30859</t>
+          <t>31030</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>30859</t>
+          <t>31030</t>
         </is>
       </c>
       <c r="J141" s="10" t="inlineStr"/>
       <c r="K141" s="11" t="inlineStr"/>
       <c r="L141" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="M141" s="10" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="N141" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="O141" s="10" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="P141" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>LIM SIEW LEE</t>
         </is>
       </c>
       <c r="Q141" s="10" t="inlineStr">
@@ -12392,12 +12392,12 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202511004</t>
+          <t>VMSB-B-202512001</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Chewy）</t>
+          <t>独家经纪合同</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
@@ -12412,12 +12412,12 @@
       </c>
       <c r="H142" s="8" t="inlineStr">
         <is>
-          <t>31032</t>
+          <t>31075</t>
         </is>
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>31032</t>
+          <t>31075</t>
         </is>
       </c>
       <c r="J142" s="8" t="inlineStr"/>
@@ -12476,17 +12476,17 @@
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202511005</t>
+          <t>VMSB-B-202601002</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Nini）</t>
+          <t>独家经纪合同（CHEONG LEI KENG) Elsa</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>2027-11-09</t>
+          <t>2028-01-05</t>
         </is>
       </c>
       <c r="G143" s="10" t="inlineStr">
@@ -12496,19 +12496,19 @@
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>31029</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
         <is>
-          <t>31029</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="J143" s="10" t="inlineStr"/>
       <c r="K143" s="11" t="inlineStr"/>
       <c r="L143" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="M143" s="10" t="inlineStr">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="N143" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="O143" s="10" t="inlineStr">
@@ -12528,7 +12528,7 @@
       </c>
       <c r="P143" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="Q143" s="10" t="inlineStr">
@@ -12560,17 +12560,17 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202511006</t>
+          <t>VMSB-O-202410001</t>
         </is>
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同</t>
+          <t>独家经纪合同 （WONG CHAI NI）Kelly</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr">
         <is>
-          <t>2027-11-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G144" s="8" t="inlineStr">
@@ -12578,41 +12578,33 @@
           <t>归档</t>
         </is>
       </c>
-      <c r="H144" s="8" t="inlineStr">
-        <is>
-          <t>31073</t>
-        </is>
-      </c>
-      <c r="I144" s="8" t="inlineStr">
-        <is>
-          <t>31073</t>
-        </is>
-      </c>
+      <c r="H144" s="8" t="inlineStr"/>
+      <c r="I144" s="8" t="inlineStr"/>
       <c r="J144" s="8" t="inlineStr"/>
       <c r="K144" s="9" t="inlineStr"/>
       <c r="L144" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>YU JING YI</t>
         </is>
       </c>
       <c r="M144" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N144" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>YU JING YI</t>
         </is>
       </c>
       <c r="O144" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P144" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q144" s="8" t="inlineStr">
@@ -12622,7 +12614,7 @@
       </c>
       <c r="R144" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -12644,17 +12636,17 @@
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202511007</t>
+          <t>VMSB-O-202410001-N</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（Mika）</t>
+          <t>艺人解除协议（双语）Wong Chai Ni</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>2027-11-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G145" s="10" t="inlineStr">
@@ -12662,41 +12654,33 @@
           <t>归档</t>
         </is>
       </c>
-      <c r="H145" s="10" t="inlineStr">
-        <is>
-          <t>31030</t>
-        </is>
-      </c>
-      <c r="I145" s="10" t="inlineStr">
-        <is>
-          <t>31030</t>
-        </is>
-      </c>
+      <c r="H145" s="10" t="n"/>
+      <c r="I145" s="10" t="n"/>
       <c r="J145" s="10" t="inlineStr"/>
       <c r="K145" s="11" t="inlineStr"/>
       <c r="L145" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>Thong Wen Yee</t>
         </is>
       </c>
       <c r="M145" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N145" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>YU JING YI</t>
         </is>
       </c>
       <c r="O145" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P145" s="10" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q145" s="10" t="inlineStr">
@@ -12706,7 +12690,7 @@
       </c>
       <c r="R145" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -12728,39 +12712,31 @@
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>VMSB-B-202512001</t>
+          <t>VMSB-O-202511001</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同</t>
+          <t>独家经纪合同（Chan Jia wen）Cheesy</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr">
         <is>
-          <t>2027-11-09</t>
+          <t>2027-09-08</t>
         </is>
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
-        </is>
-      </c>
-      <c r="H146" s="8" t="inlineStr">
-        <is>
-          <t>31075</t>
-        </is>
-      </c>
-      <c r="I146" s="8" t="inlineStr">
-        <is>
-          <t>31075</t>
-        </is>
-      </c>
+          <t>用印</t>
+        </is>
+      </c>
+      <c r="H146" s="8" t="inlineStr"/>
+      <c r="I146" s="8" t="inlineStr"/>
       <c r="J146" s="8" t="inlineStr"/>
       <c r="K146" s="9" t="inlineStr"/>
       <c r="L146" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="M146" s="8" t="inlineStr">
@@ -12770,7 +12746,7 @@
       </c>
       <c r="N146" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="O146" s="8" t="inlineStr">
@@ -12780,7 +12756,7 @@
       </c>
       <c r="P146" s="8" t="inlineStr">
         <is>
-          <t>LIM SIEW LEE</t>
+          <t>CHOU YINING</t>
         </is>
       </c>
       <c r="Q146" s="8" t="inlineStr">
@@ -12812,34 +12788,26 @@
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>VMSB-B-202601002</t>
+          <t>VMSB-O-202604001</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（CHEONG LEI KENG) Elsa</t>
+          <t>MZ9M 33 独家经纪约（三三）</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>2028-01-05</t>
+          <t>2028-03-17</t>
         </is>
       </c>
       <c r="G147" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
-        </is>
-      </c>
-      <c r="H147" s="10" t="inlineStr">
-        <is>
-          <t>28947</t>
-        </is>
-      </c>
-      <c r="I147" s="10" t="inlineStr">
-        <is>
-          <t>28947</t>
-        </is>
-      </c>
+          <t>上传电子档</t>
+        </is>
+      </c>
+      <c r="H147" s="10" t="inlineStr"/>
+      <c r="I147" s="10" t="inlineStr"/>
       <c r="J147" s="10" t="inlineStr"/>
       <c r="K147" s="11" t="inlineStr"/>
       <c r="L147" s="10" t="inlineStr">
@@ -12896,17 +12864,17 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>VMSB-O-202410001</t>
+          <t>XF-B-202401001</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同 （WONG CHAI NI）Kelly</t>
+          <t>抖音-游戏-剑纯【沈舒晗】独家经纪约-三年</t>
         </is>
       </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="G148" s="8" t="inlineStr">
@@ -12914,33 +12882,41 @@
           <t>归档</t>
         </is>
       </c>
-      <c r="H148" s="8" t="inlineStr"/>
-      <c r="I148" s="8" t="inlineStr"/>
+      <c r="H148" s="8" t="inlineStr">
+        <is>
+          <t>27559</t>
+        </is>
+      </c>
+      <c r="I148" s="8" t="inlineStr">
+        <is>
+          <t>27559</t>
+        </is>
+      </c>
       <c r="J148" s="8" t="inlineStr"/>
       <c r="K148" s="9" t="inlineStr"/>
       <c r="L148" s="8" t="inlineStr">
         <is>
-          <t>YU JING YI</t>
+          <t>区景桉</t>
         </is>
       </c>
       <c r="M148" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N148" s="8" t="inlineStr">
         <is>
-          <t>YU JING YI</t>
+          <t>区景桉</t>
         </is>
       </c>
       <c r="O148" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P148" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>区景桉</t>
         </is>
       </c>
       <c r="Q148" s="8" t="inlineStr">
@@ -12950,7 +12926,7 @@
       </c>
       <c r="R148" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -12972,17 +12948,17 @@
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>VMSB-O-202410001-N</t>
+          <t>XF-B-202401006</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>艺人解除协议（双语）Wong Chai Ni</t>
+          <t>独家经纪合同-西伐-叶芳盏_霜霜_经纪约-20240110</t>
         </is>
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G149" s="10" t="inlineStr">
@@ -12990,33 +12966,41 @@
           <t>归档</t>
         </is>
       </c>
-      <c r="H149" s="10" t="n"/>
-      <c r="I149" s="10" t="n"/>
+      <c r="H149" s="10" t="inlineStr">
+        <is>
+          <t>15120</t>
+        </is>
+      </c>
+      <c r="I149" s="10" t="inlineStr">
+        <is>
+          <t>15120</t>
+        </is>
+      </c>
       <c r="J149" s="10" t="inlineStr"/>
       <c r="K149" s="11" t="inlineStr"/>
       <c r="L149" s="10" t="inlineStr">
         <is>
-          <t>Thong Wen Yee</t>
+          <t>区景桉</t>
         </is>
       </c>
       <c r="M149" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N149" s="10" t="inlineStr">
         <is>
-          <t>YU JING YI</t>
+          <t>区景桉</t>
         </is>
       </c>
       <c r="O149" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P149" s="10" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>区景桉</t>
         </is>
       </c>
       <c r="Q149" s="10" t="inlineStr">
@@ -13026,7 +13010,7 @@
       </c>
       <c r="R149" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -13048,31 +13032,39 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>VMSB-O-202511001</t>
+          <t>XF-B-202401008</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同（Chan Jia wen）Cheesy</t>
+          <t>抖音-王者-闪光独家经纪合同【抖音】</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
         <is>
-          <t>2027-09-08</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>用印</t>
-        </is>
-      </c>
-      <c r="H150" s="8" t="inlineStr"/>
-      <c r="I150" s="8" t="inlineStr"/>
+          <t>归档</t>
+        </is>
+      </c>
+      <c r="H150" s="8" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="I150" s="8" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
       <c r="J150" s="8" t="inlineStr"/>
       <c r="K150" s="9" t="inlineStr"/>
       <c r="L150" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="M150" s="8" t="inlineStr">
@@ -13082,17 +13074,17 @@
       </c>
       <c r="N150" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>陈尧</t>
         </is>
       </c>
       <c r="O150" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P150" s="8" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="Q150" s="8" t="inlineStr">
@@ -13124,31 +13116,39 @@
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>VMSB-O-202604001</t>
+          <t>XF-B-202401009</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>MZ9M 33 独家经纪约（三三）</t>
+          <t>抖音-游戏-筱七商务&amp;自媒体独家经纪合同</t>
         </is>
       </c>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>2028-03-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G151" s="10" t="inlineStr">
         <is>
-          <t>上传电子档</t>
-        </is>
-      </c>
-      <c r="H151" s="10" t="inlineStr"/>
-      <c r="I151" s="10" t="inlineStr"/>
+          <t>归档</t>
+        </is>
+      </c>
+      <c r="H151" s="10" t="inlineStr">
+        <is>
+          <t>28082</t>
+        </is>
+      </c>
+      <c r="I151" s="10" t="inlineStr">
+        <is>
+          <t>28082</t>
+        </is>
+      </c>
       <c r="J151" s="10" t="inlineStr"/>
       <c r="K151" s="11" t="inlineStr"/>
       <c r="L151" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="M151" s="10" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="N151" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="O151" s="10" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="P151" s="10" t="inlineStr">
         <is>
-          <t>CHOU YINING</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="Q151" s="10" t="inlineStr">
@@ -13200,17 +13200,17 @@
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202401001</t>
+          <t>XF-B-202401009-N</t>
         </is>
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>抖音-游戏-剑纯【沈舒晗】独家经纪约-三年</t>
+          <t>抖音-游戏-筱七独家经纪解除协议</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G152" s="8" t="inlineStr">
@@ -13220,19 +13220,19 @@
       </c>
       <c r="H152" s="8" t="inlineStr">
         <is>
-          <t>27559</t>
+          <t>28082</t>
         </is>
       </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
-          <t>27559</t>
+          <t>28082</t>
         </is>
       </c>
       <c r="J152" s="8" t="inlineStr"/>
       <c r="K152" s="9" t="inlineStr"/>
       <c r="L152" s="8" t="inlineStr">
         <is>
-          <t>区景桉</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="M152" s="8" t="inlineStr">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="N152" s="8" t="inlineStr">
         <is>
-          <t>区景桉</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="O152" s="8" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="P152" s="8" t="inlineStr">
         <is>
-          <t>区景桉</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="Q152" s="8" t="inlineStr">
@@ -13284,39 +13284,39 @@
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202401006</t>
+          <t>XF-B-202403001</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-西伐-叶芳盏_霜霜_经纪约-20240110</t>
+          <t>抖音-游戏-余生一个小浪浪独家经纪协议</t>
         </is>
       </c>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G153" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>28254</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>28254</t>
         </is>
       </c>
       <c r="J153" s="10" t="inlineStr"/>
       <c r="K153" s="11" t="inlineStr"/>
       <c r="L153" s="10" t="inlineStr">
         <is>
-          <t>区景桉</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="M153" s="10" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="N153" s="10" t="inlineStr">
         <is>
-          <t>区景桉</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="O153" s="10" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="P153" s="10" t="inlineStr">
         <is>
-          <t>区景桉</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="Q153" s="10" t="inlineStr">
@@ -13368,17 +13368,17 @@
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202401008</t>
+          <t>XF-B-202404003</t>
         </is>
       </c>
       <c r="E154" s="9" t="inlineStr">
         <is>
-          <t>抖音-王者-闪光独家经纪合同【抖音】</t>
+          <t>抖音-游戏-真真酱独家经纪合同</t>
         </is>
       </c>
       <c r="F154" s="8" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G154" s="8" t="inlineStr">
@@ -13388,12 +13388,12 @@
       </c>
       <c r="H154" s="8" t="inlineStr">
         <is>
-          <t>27842</t>
+          <t>28354</t>
         </is>
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>27842</t>
+          <t>28354</t>
         </is>
       </c>
       <c r="J154" s="8" t="inlineStr"/>
@@ -13410,12 +13410,12 @@
       </c>
       <c r="N154" s="8" t="inlineStr">
         <is>
-          <t>陈尧</t>
+          <t>黎小飞</t>
         </is>
       </c>
       <c r="O154" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P154" s="8" t="inlineStr">
@@ -13452,17 +13452,17 @@
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202401009</t>
+          <t>XF-B-202404003-N</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>抖音-游戏-筱七商务&amp;自媒体独家经纪合同</t>
+          <t>抖音-游戏-真真经纪解除协议</t>
         </is>
       </c>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G155" s="10" t="inlineStr">
@@ -13472,12 +13472,12 @@
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>28082</t>
+          <t>28354</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
-          <t>28082</t>
+          <t>28354</t>
         </is>
       </c>
       <c r="J155" s="10" t="inlineStr"/>
@@ -13536,17 +13536,17 @@
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202401009-N</t>
+          <t>XF-B-202404003-S1</t>
         </is>
       </c>
       <c r="E156" s="9" t="inlineStr">
         <is>
-          <t>抖音-游戏-筱七独家经纪解除协议</t>
+          <t>抖音-游戏-真真酱独家经纪补充协议之一</t>
         </is>
       </c>
       <c r="F156" s="8" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G156" s="8" t="inlineStr">
@@ -13556,12 +13556,12 @@
       </c>
       <c r="H156" s="8" t="inlineStr">
         <is>
-          <t>28082</t>
+          <t>28354</t>
         </is>
       </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>28082</t>
+          <t>28354</t>
         </is>
       </c>
       <c r="J156" s="8" t="inlineStr"/>
@@ -13620,32 +13620,32 @@
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202403001</t>
+          <t>XF-B-202404005</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>抖音-游戏-余生一个小浪浪独家经纪协议</t>
+          <t>抖音-游戏-芝芝经纪协议</t>
         </is>
       </c>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G157" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="J157" s="10" t="inlineStr"/>
@@ -13704,17 +13704,17 @@
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202404003</t>
+          <t>XF-B-202404005-N</t>
         </is>
       </c>
       <c r="E158" s="9" t="inlineStr">
         <is>
-          <t>抖音-游戏-真真酱独家经纪合同</t>
+          <t>抖音-游戏-芝芝经纪解除协议</t>
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G158" s="8" t="inlineStr">
@@ -13724,12 +13724,12 @@
       </c>
       <c r="H158" s="8" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="J158" s="8" t="inlineStr"/>
@@ -13788,12 +13788,12 @@
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202404003-N</t>
+          <t>XF-B-202404007</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>抖音-游戏-真真经纪解除协议</t>
+          <t>抖音-游戏-陈楚云独家经纪合同</t>
         </is>
       </c>
       <c r="F159" s="10" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="H159" s="10" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="J159" s="10" t="inlineStr"/>
@@ -13872,17 +13872,17 @@
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202404003-S1</t>
+          <t>XF-B-202404007-N</t>
         </is>
       </c>
       <c r="E160" s="9" t="inlineStr">
         <is>
-          <t>抖音-游戏-真真酱独家经纪补充协议之一</t>
+          <t>抖音-游戏-陈楚云解除协议</t>
         </is>
       </c>
       <c r="F160" s="8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G160" s="8" t="inlineStr">
@@ -13892,12 +13892,12 @@
       </c>
       <c r="H160" s="8" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="J160" s="8" t="inlineStr"/>
@@ -13956,39 +13956,39 @@
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202404005</t>
+          <t>XF-B-202412001</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>抖音-游戏-芝芝经纪协议</t>
+          <t>西伐-逐浪抖音-李尚-王者-20241101</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="G161" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>申请人确认签约性质</t>
         </is>
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="J161" s="10" t="inlineStr"/>
       <c r="K161" s="11" t="inlineStr"/>
       <c r="L161" s="10" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>何嘉伟</t>
         </is>
       </c>
       <c r="M161" s="10" t="inlineStr">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="N161" s="10" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>何嘉伟</t>
         </is>
       </c>
       <c r="O161" s="10" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="P161" s="10" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>何嘉伟</t>
         </is>
       </c>
       <c r="Q161" s="10" t="inlineStr">
@@ -14040,17 +14040,17 @@
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202404005-N</t>
+          <t>XF-B-202412001-N</t>
         </is>
       </c>
       <c r="E162" s="9" t="inlineStr">
         <is>
-          <t>抖音-游戏-芝芝经纪解除协议</t>
+          <t>抖音-游戏-李尚经纪解除协议</t>
         </is>
       </c>
       <c r="F162" s="8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="G162" s="8" t="inlineStr">
@@ -14060,12 +14060,12 @@
       </c>
       <c r="H162" s="8" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr"/>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="N162" s="8" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>何嘉伟</t>
         </is>
       </c>
       <c r="O162" s="8" t="inlineStr">
@@ -14124,17 +14124,17 @@
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202404007</t>
+          <t>XF-J-202401001</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>抖音-游戏-陈楚云独家经纪合同</t>
+          <t>游戏-抖音-西伐&amp;武汉弈极联合运营合同</t>
         </is>
       </c>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="G163" s="10" t="inlineStr">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>27565</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>27565</t>
         </is>
       </c>
       <c r="J163" s="10" t="inlineStr"/>
@@ -14208,17 +14208,17 @@
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202404007-N</t>
+          <t>XJ-B-202205001</t>
         </is>
       </c>
       <c r="E164" s="9" t="inlineStr">
         <is>
-          <t>抖音-游戏-陈楚云解除协议</t>
+          <t>独家经纪合同-赵豪（解说嘉豪）</t>
         </is>
       </c>
       <c r="F164" s="8" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2027-05-14</t>
         </is>
       </c>
       <c r="G164" s="8" t="inlineStr">
@@ -14228,39 +14228,39 @@
       </c>
       <c r="H164" s="8" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>19801</t>
         </is>
       </c>
       <c r="I164" s="8" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>19801</t>
         </is>
       </c>
       <c r="J164" s="8" t="inlineStr"/>
       <c r="K164" s="9" t="inlineStr"/>
       <c r="L164" s="8" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>叶睿</t>
         </is>
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N164" s="8" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>叶睿</t>
         </is>
       </c>
       <c r="O164" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P164" s="8" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q164" s="8" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="R164" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -14292,59 +14292,59 @@
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>XF-B-202412001</t>
+          <t>XJ-B-202206002</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>西伐-逐浪抖音-李尚-王者-20241101</t>
+          <t>独家经纪合同-叶骏成</t>
         </is>
       </c>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2027-06-26</t>
         </is>
       </c>
       <c r="G165" s="10" t="inlineStr">
         <is>
-          <t>申请人确认签约性质</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H165" s="10" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="J165" s="10" t="inlineStr"/>
       <c r="K165" s="11" t="inlineStr"/>
       <c r="L165" s="10" t="inlineStr">
         <is>
-          <t>何嘉伟</t>
+          <t>叶睿</t>
         </is>
       </c>
       <c r="M165" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N165" s="10" t="inlineStr">
         <is>
-          <t>何嘉伟</t>
+          <t>叶睿</t>
         </is>
       </c>
       <c r="O165" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P165" s="10" t="inlineStr">
         <is>
-          <t>何嘉伟</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q165" s="10" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="R165" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -14376,17 +14376,17 @@
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>XF-B-202412001-N</t>
+          <t>XJ-B-202206002-N</t>
         </is>
       </c>
       <c r="E166" s="9" t="inlineStr">
         <is>
-          <t>抖音-游戏-李尚经纪解除协议</t>
+          <t>【香蕉】艺人经纪约解约协议（解说叶骏成）</t>
         </is>
       </c>
       <c r="F166" s="8" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2027-06-26</t>
         </is>
       </c>
       <c r="G166" s="8" t="inlineStr">
@@ -14396,39 +14396,39 @@
       </c>
       <c r="H166" s="8" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="I166" s="8" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="J166" s="8" t="inlineStr"/>
       <c r="K166" s="9" t="inlineStr"/>
       <c r="L166" s="8" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>金佳冬</t>
         </is>
       </c>
       <c r="M166" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N166" s="8" t="inlineStr">
         <is>
-          <t>何嘉伟</t>
+          <t>叶睿</t>
         </is>
       </c>
       <c r="O166" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P166" s="8" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q166" s="8" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="R166" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -14460,17 +14460,17 @@
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>XF-J-202401001</t>
+          <t>XJ-B-202206003</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>游戏-抖音-西伐&amp;武汉弈极联合运营合同</t>
+          <t>独家经纪合同-吴均远（解说均远）</t>
         </is>
       </c>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-05-31</t>
         </is>
       </c>
       <c r="G167" s="10" t="inlineStr">
@@ -14480,39 +14480,39 @@
       </c>
       <c r="H167" s="10" t="inlineStr">
         <is>
-          <t>27565</t>
+          <t>21738</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr">
         <is>
-          <t>27565</t>
+          <t>21738</t>
         </is>
       </c>
       <c r="J167" s="10" t="inlineStr"/>
       <c r="K167" s="11" t="inlineStr"/>
       <c r="L167" s="10" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>叶睿</t>
         </is>
       </c>
       <c r="M167" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N167" s="10" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>叶睿</t>
         </is>
       </c>
       <c r="O167" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P167" s="10" t="inlineStr">
         <is>
-          <t>黎小飞</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q167" s="10" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="R167" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -14544,17 +14544,17 @@
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202205001</t>
+          <t>XJ-B-202206003-S1</t>
         </is>
       </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-赵豪（解说嘉豪）</t>
+          <t>独家经纪合同-吴均远-补充协议</t>
         </is>
       </c>
       <c r="F168" s="8" t="inlineStr">
         <is>
-          <t>2027-05-14</t>
+          <t>2027-05-31</t>
         </is>
       </c>
       <c r="G168" s="8" t="inlineStr">
@@ -14564,19 +14564,19 @@
       </c>
       <c r="H168" s="8" t="inlineStr">
         <is>
-          <t>19801</t>
+          <t>21738</t>
         </is>
       </c>
       <c r="I168" s="8" t="inlineStr">
         <is>
-          <t>19801</t>
+          <t>21738</t>
         </is>
       </c>
       <c r="J168" s="8" t="inlineStr"/>
       <c r="K168" s="9" t="inlineStr"/>
       <c r="L168" s="8" t="inlineStr">
         <is>
-          <t>叶睿</t>
+          <t>彭星月</t>
         </is>
       </c>
       <c r="M168" s="8" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="N168" s="8" t="inlineStr">
         <is>
-          <t>叶睿</t>
+          <t>彭星月</t>
         </is>
       </c>
       <c r="O168" s="8" t="inlineStr">
@@ -14628,17 +14628,17 @@
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202206002</t>
+          <t>XJ-B-202302003</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-叶骏成</t>
+          <t>独家经纪合同（覃尚）</t>
         </is>
       </c>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>2027-06-26</t>
+          <t>2028-02-28</t>
         </is>
       </c>
       <c r="G169" s="10" t="inlineStr">
@@ -14648,39 +14648,39 @@
       </c>
       <c r="H169" s="10" t="inlineStr">
         <is>
-          <t>21680</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="I169" s="10" t="inlineStr">
         <is>
-          <t>21680</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="J169" s="10" t="inlineStr"/>
       <c r="K169" s="11" t="inlineStr"/>
       <c r="L169" s="10" t="inlineStr">
         <is>
-          <t>叶睿</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="M169" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N169" s="10" t="inlineStr">
         <is>
-          <t>叶睿</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="O169" s="10" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P169" s="10" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="Q169" s="10" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="R169" s="11" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -14712,17 +14712,17 @@
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202206002-N</t>
+          <t>XJ-B-202303001</t>
         </is>
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>【香蕉】艺人经纪约解约协议（解说叶骏成）</t>
+          <t>郭妃妤独家经纪合同</t>
         </is>
       </c>
       <c r="F170" s="8" t="inlineStr">
         <is>
-          <t>2027-06-26</t>
+          <t>2028-03-31</t>
         </is>
       </c>
       <c r="G170" s="8" t="inlineStr">
@@ -14732,39 +14732,39 @@
       </c>
       <c r="H170" s="8" t="inlineStr">
         <is>
-          <t>21680</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="I170" s="8" t="inlineStr">
         <is>
-          <t>21680</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="J170" s="8" t="inlineStr"/>
       <c r="K170" s="9" t="inlineStr"/>
       <c r="L170" s="8" t="inlineStr">
         <is>
-          <t>金佳冬</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="N170" s="8" t="inlineStr">
         <is>
-          <t>叶睿</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="O170" s="8" t="inlineStr">
         <is>
-          <t>离职</t>
+          <t>在职</t>
         </is>
       </c>
       <c r="P170" s="8" t="inlineStr">
         <is>
-          <t>李家琪</t>
+          <t>陈雨婷</t>
         </is>
       </c>
       <c r="Q170" s="8" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="R170" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
+          <t>申请人/创建人在职或未确认离职,无需调整</t>
         </is>
       </c>
     </row>
@@ -14796,17 +14796,17 @@
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202206003</t>
+          <t>XJ-B-202303002</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-吴均远（解说均远）</t>
+          <t>独家经纪合同-神乐</t>
         </is>
       </c>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>2027-05-31</t>
+          <t>2028-03-22</t>
         </is>
       </c>
       <c r="G171" s="10" t="inlineStr">
@@ -14816,19 +14816,19 @@
       </c>
       <c r="H171" s="10" t="inlineStr">
         <is>
-          <t>21738</t>
+          <t>24429</t>
         </is>
       </c>
       <c r="I171" s="10" t="inlineStr">
         <is>
-          <t>21738</t>
+          <t>24429</t>
         </is>
       </c>
       <c r="J171" s="10" t="inlineStr"/>
       <c r="K171" s="11" t="inlineStr"/>
       <c r="L171" s="10" t="inlineStr">
         <is>
-          <t>叶睿</t>
+          <t>彭星月</t>
         </is>
       </c>
       <c r="M171" s="10" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="N171" s="10" t="inlineStr">
         <is>
-          <t>叶睿</t>
+          <t>彭星月</t>
         </is>
       </c>
       <c r="O171" s="10" t="inlineStr">
@@ -14880,17 +14880,17 @@
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202206003-S1</t>
+          <t>XJ-B-202306001</t>
         </is>
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同-吴均远-补充协议</t>
+          <t>独家经纪合同--七之宝</t>
         </is>
       </c>
       <c r="F172" s="8" t="inlineStr">
         <is>
-          <t>2027-05-31</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G172" s="8" t="inlineStr">
@@ -14900,12 +14900,12 @@
       </c>
       <c r="H172" s="8" t="inlineStr">
         <is>
-          <t>21738</t>
+          <t>24891</t>
         </is>
       </c>
       <c r="I172" s="8" t="inlineStr">
         <is>
-          <t>21738</t>
+          <t>24891</t>
         </is>
       </c>
       <c r="J172" s="8" t="inlineStr"/>
@@ -14964,17 +14964,17 @@
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202302003</t>
+          <t>XJ-B-202306003</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同（覃尚）</t>
+          <t>独家经纪合同-严友浩</t>
         </is>
       </c>
       <c r="F173" s="10" t="inlineStr">
         <is>
-          <t>2028-02-28</t>
+          <t>2028-06-20</t>
         </is>
       </c>
       <c r="G173" s="10" t="inlineStr">
@@ -14984,39 +14984,39 @@
       </c>
       <c r="H173" s="10" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>24948</t>
         </is>
       </c>
       <c r="I173" s="10" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>24948</t>
         </is>
       </c>
       <c r="J173" s="10" t="inlineStr"/>
       <c r="K173" s="11" t="inlineStr"/>
       <c r="L173" s="10" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>彭星月</t>
         </is>
       </c>
       <c r="M173" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="N173" s="10" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>彭星月</t>
         </is>
       </c>
       <c r="O173" s="10" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P173" s="10" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q173" s="10" t="inlineStr">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="R173" s="11" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -15048,61 +15048,61 @@
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202303001</t>
+          <t>XJ-B-202307001</t>
         </is>
       </c>
       <c r="E174" s="9" t="inlineStr">
         <is>
-          <t>郭妃妤独家经纪合同</t>
+          <t>圈圈独家经纪合同</t>
         </is>
       </c>
       <c r="F174" s="8" t="inlineStr">
         <is>
-          <t>2028-03-31</t>
+          <t>2028-06-30</t>
         </is>
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H174" s="8" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="I174" s="8" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="J174" s="8" t="inlineStr"/>
       <c r="K174" s="9" t="inlineStr"/>
       <c r="L174" s="8" t="inlineStr">
         <is>
+          <t>蔡译凡</t>
+        </is>
+      </c>
+      <c r="M174" s="8" t="inlineStr">
+        <is>
+          <t>离职</t>
+        </is>
+      </c>
+      <c r="N174" s="8" t="inlineStr">
+        <is>
           <t>陈雨婷</t>
         </is>
       </c>
-      <c r="M174" s="8" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
-      <c r="N174" s="8" t="inlineStr">
+      <c r="O174" s="8" t="inlineStr">
+        <is>
+          <t>在职</t>
+        </is>
+      </c>
+      <c r="P174" s="8" t="inlineStr">
         <is>
           <t>陈雨婷</t>
         </is>
       </c>
-      <c r="O174" s="8" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
-      <c r="P174" s="8" t="inlineStr">
-        <is>
-          <t>陈雨婷</t>
-        </is>
-      </c>
       <c r="Q174" s="8" t="inlineStr">
         <is>
           <t>在职</t>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="R174" s="9" t="inlineStr">
         <is>
-          <t>申请人/创建人在职或未确认离职,无需调整</t>
+          <t>申请人离职,更新为合同执行人</t>
         </is>
       </c>
     </row>
@@ -15132,17 +15132,17 @@
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202303002</t>
+          <t>XJ-B-202307003</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-神乐</t>
+          <t>Doby_独家经纪合同（通用版）_20230221_V2.3</t>
         </is>
       </c>
       <c r="F175" s="10" t="inlineStr">
         <is>
-          <t>2028-03-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G175" s="10" t="inlineStr">
@@ -15152,19 +15152,19 @@
       </c>
       <c r="H175" s="10" t="inlineStr">
         <is>
-          <t>24429</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr">
         <is>
-          <t>24429</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="J175" s="10" t="inlineStr"/>
       <c r="K175" s="11" t="inlineStr"/>
       <c r="L175" s="10" t="inlineStr">
         <is>
-          <t>彭星月</t>
+          <t>宋頔斐</t>
         </is>
       </c>
       <c r="M175" s="10" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="N175" s="10" t="inlineStr">
         <is>
-          <t>彭星月</t>
+          <t>宋頔斐</t>
         </is>
       </c>
       <c r="O175" s="10" t="inlineStr">
@@ -15216,17 +15216,17 @@
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202306001</t>
+          <t>XJ-B-202307004</t>
         </is>
       </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
-          <t>独家经纪合同--七之宝</t>
+          <t>童童_独家经纪合同（通用版）_20230221_V2.3</t>
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G176" s="8" t="inlineStr">
@@ -15236,19 +15236,19 @@
       </c>
       <c r="H176" s="8" t="inlineStr">
         <is>
-          <t>24891</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="I176" s="8" t="inlineStr">
         <is>
-          <t>24891</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="J176" s="8" t="inlineStr"/>
       <c r="K176" s="9" t="inlineStr"/>
       <c r="L176" s="8" t="inlineStr">
         <is>
-          <t>彭星月</t>
+          <t>宋頔斐</t>
         </is>
       </c>
       <c r="M176" s="8" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="N176" s="8" t="inlineStr">
         <is>
-          <t>彭星月</t>
+          <t>宋頔斐</t>
         </is>
       </c>
       <c r="O176" s="8" t="inlineStr">
@@ -15300,17 +15300,17 @@
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202306003</t>
+          <t>XJ-B-202307005</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
         <is>
-          <t>独家经纪合同-严友浩</t>
+          <t>卡凡独家经纪合同</t>
         </is>
       </c>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>2028-06-20</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G177" s="10" t="inlineStr">
@@ -15320,19 +15320,19 @@
       </c>
       <c r="H177" s="10" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="J177" s="10" t="inlineStr"/>
       <c r="K177" s="11" t="inlineStr"/>
       <c r="L177" s="10" t="inlineStr">
         <is>
-          <t>彭星月</t>
+          <t>蔡译凡</t>
         </is>
       </c>
       <c r="M177" s="10" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="N177" s="10" t="inlineStr">
         <is>
-          <t>彭星月</t>
+          <t>蔡译凡</t>
         </is>
       </c>
       <c r="O177" s="10" t="inlineStr">
@@ -15384,39 +15384,39 @@
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202307001</t>
+          <t>XJ-B-202307006</t>
         </is>
       </c>
       <c r="E178" s="9" t="inlineStr">
         <is>
-          <t>圈圈独家经纪合同</t>
+          <t>Yoho_独家经纪合同（通用版）_20230221_V2.3</t>
         </is>
       </c>
       <c r="F178" s="8" t="inlineStr">
         <is>
-          <t>2028-06-30</t>
+          <t>2028-07-31</t>
         </is>
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H178" s="8" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>26545</t>
         </is>
       </c>
       <c r="I178" s="8" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>26545</t>
         </is>
       </c>
       <c r="J178" s="8" t="inlineStr"/>
       <c r="K178" s="9" t="inlineStr"/>
       <c r="L178" s="8" t="inlineStr">
         <is>
-          <t>蔡译凡</t>
+          <t>宋頔斐</t>
         </is>
       </c>
       <c r="M178" s="8" t="inlineStr">
@@ -15426,17 +15426,17 @@
       </c>
       <c r="N178" s="8" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>宋頔斐</t>
         </is>
       </c>
       <c r="O178" s="8" t="inlineStr">
         <is>
-          <t>在职</t>
+          <t>离职</t>
         </is>
       </c>
       <c r="P178" s="8" t="inlineStr">
         <is>
-          <t>陈雨婷</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q178" s="8" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="R178" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,更新为合同执行人</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
@@ -15468,17 +15468,17 @@
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202307003</t>
+          <t>XJ-B-202308001</t>
         </is>
       </c>
       <c r="E179" s="11" t="inlineStr">
         <is>
-          <t>Doby_独家经纪合同（通用版）_20230221_V2.3</t>
+          <t>Fly_独家经纪合同（通用版）_20230221_V2.3</t>
         </is>
       </c>
       <c r="F179" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2028-08-03</t>
         </is>
       </c>
       <c r="G179" s="10" t="inlineStr">
@@ -15488,12 +15488,12 @@
       </c>
       <c r="H179" s="10" t="inlineStr">
         <is>
-          <t>26537</t>
+          <t>26587</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr">
         <is>
-          <t>26537</t>
+          <t>26587</t>
         </is>
       </c>
       <c r="J179" s="10" t="inlineStr"/>
@@ -15552,39 +15552,39 @@
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202307004</t>
+          <t>XJ-B-202308002</t>
         </is>
       </c>
       <c r="E180" s="9" t="inlineStr">
         <is>
-          <t>童童_独家经纪合同（通用版）_20230221_V2.3</t>
+          <t>VSPO独家经纪合同-张语希</t>
         </is>
       </c>
       <c r="F180" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2028-09-01</t>
         </is>
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>用印</t>
         </is>
       </c>
       <c r="H180" s="8" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>26769</t>
         </is>
       </c>
       <c r="I180" s="8" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>26769</t>
         </is>
       </c>
       <c r="J180" s="8" t="inlineStr"/>
       <c r="K180" s="9" t="inlineStr"/>
       <c r="L180" s="8" t="inlineStr">
         <is>
-          <t>宋頔斐</t>
+          <t>徐如珺</t>
         </is>
       </c>
       <c r="M180" s="8" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="N180" s="8" t="inlineStr">
         <is>
-          <t>宋頔斐</t>
+          <t>徐如珺</t>
         </is>
       </c>
       <c r="O180" s="8" t="inlineStr">
@@ -15636,39 +15636,39 @@
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202307005</t>
+          <t>XJ-B-202309002</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
         <is>
-          <t>卡凡独家经纪合同</t>
+          <t>【香蕉】VSPO独家经纪合同-逗木doumu</t>
         </is>
       </c>
       <c r="F181" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G181" s="10" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>上传电子档</t>
         </is>
       </c>
       <c r="H181" s="10" t="inlineStr">
         <is>
-          <t>26557</t>
+          <t>26813</t>
         </is>
       </c>
       <c r="I181" s="10" t="inlineStr">
         <is>
-          <t>26557</t>
+          <t>26813</t>
         </is>
       </c>
       <c r="J181" s="10" t="inlineStr"/>
       <c r="K181" s="11" t="inlineStr"/>
       <c r="L181" s="10" t="inlineStr">
         <is>
-          <t>蔡译凡</t>
+          <t>徐如珺</t>
         </is>
       </c>
       <c r="M181" s="10" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="N181" s="10" t="inlineStr">
         <is>
-          <t>蔡译凡</t>
+          <t>徐如珺</t>
         </is>
       </c>
       <c r="O181" s="10" t="inlineStr">
@@ -15720,39 +15720,39 @@
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202307006</t>
+          <t>XJ-B-202311001</t>
         </is>
       </c>
       <c r="E182" s="9" t="inlineStr">
         <is>
-          <t>Yoho_独家经纪合同（通用版）_20230221_V2.3</t>
+          <t>《香蕉》徐培博独家经济合同</t>
         </is>
       </c>
       <c r="F182" s="8" t="inlineStr">
         <is>
-          <t>2028-07-31</t>
+          <t>2028-06-20</t>
         </is>
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>法务确认</t>
         </is>
       </c>
       <c r="H182" s="8" t="inlineStr">
         <is>
-          <t>26545</t>
+          <t>27115</t>
         </is>
       </c>
       <c r="I182" s="8" t="inlineStr">
         <is>
-          <t>26545</t>
+          <t>27115</t>
         </is>
       </c>
       <c r="J182" s="8" t="inlineStr"/>
       <c r="K182" s="9" t="inlineStr"/>
       <c r="L182" s="8" t="inlineStr">
         <is>
-          <t>宋頔斐</t>
+          <t>吴均远</t>
         </is>
       </c>
       <c r="M182" s="8" t="inlineStr">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="N182" s="8" t="inlineStr">
         <is>
-          <t>宋頔斐</t>
+          <t>徐如珺1</t>
         </is>
       </c>
       <c r="O182" s="8" t="inlineStr">
@@ -15804,17 +15804,17 @@
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>XJ-B-202308001</t>
+          <t>XJ-B-202401001</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
         <is>
-          <t>Fly_独家经纪合同（通用版）_20230221_V2.3</t>
+          <t>重越_独家经纪合同（通用版）_20230221_V2.3</t>
         </is>
       </c>
       <c r="F183" s="10" t="inlineStr">
         <is>
-          <t>2028-08-03</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="G183" s="10" t="inlineStr">
@@ -15824,12 +15824,12 @@
       </c>
       <c r="H183" s="10" t="inlineStr">
         <is>
-          <t>26587</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="I183" s="10" t="inlineStr">
         <is>
-          <t>26587</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="J183" s="10" t="inlineStr"/>
@@ -15888,39 +15888,39 @@
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>XJ-B-202308002</t>
+          <t>XJ-B-202402001</t>
         </is>
       </c>
       <c r="E184" s="9" t="inlineStr">
         <is>
-          <t>VSPO独家经纪合同-张语希</t>
+          <t>王梓源_独家经纪合同（通用版）_20230221_V2.3</t>
         </is>
       </c>
       <c r="F184" s="8" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2029-02-28</t>
         </is>
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t>用印</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="H184" s="8" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>28224</t>
         </is>
       </c>
       <c r="I184" s="8" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>28224</t>
         </is>
       </c>
       <c r="J184" s="8" t="inlineStr"/>
       <c r="K184" s="9" t="inlineStr"/>
       <c r="L184" s="8" t="inlineStr">
         <is>
-          <t>徐如珺</t>
+          <t>宋頔斐1</t>
         </is>
       </c>
       <c r="M184" s="8" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="N184" s="8" t="inlineStr">
         <is>
-          <t>徐如珺</t>
+          <t>宋頔斐1</t>
         </is>
       </c>
       <c r="O184" s="8" t="inlineStr">
@@ -15954,344 +15954,8 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="B185" s="10" t="inlineStr">
-        <is>
-          <t>未发生替换仍未命中Hand</t>
-        </is>
-      </c>
-      <c r="C185" s="10" t="inlineStr">
-        <is>
-          <t>Hand生产库未命中</t>
-        </is>
-      </c>
-      <c r="D185" s="10" t="inlineStr">
-        <is>
-          <t>XJ-B-202309002</t>
-        </is>
-      </c>
-      <c r="E185" s="11" t="inlineStr">
-        <is>
-          <t>【香蕉】VSPO独家经纪合同-逗木doumu</t>
-        </is>
-      </c>
-      <c r="F185" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G185" s="10" t="inlineStr">
-        <is>
-          <t>上传电子档</t>
-        </is>
-      </c>
-      <c r="H185" s="10" t="inlineStr">
-        <is>
-          <t>26813</t>
-        </is>
-      </c>
-      <c r="I185" s="10" t="inlineStr">
-        <is>
-          <t>26813</t>
-        </is>
-      </c>
-      <c r="J185" s="10" t="inlineStr"/>
-      <c r="K185" s="11" t="inlineStr"/>
-      <c r="L185" s="10" t="inlineStr">
-        <is>
-          <t>徐如珺</t>
-        </is>
-      </c>
-      <c r="M185" s="10" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
-      <c r="N185" s="10" t="inlineStr">
-        <is>
-          <t>徐如珺</t>
-        </is>
-      </c>
-      <c r="O185" s="10" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
-      <c r="P185" s="10" t="inlineStr">
-        <is>
-          <t>李家琪</t>
-        </is>
-      </c>
-      <c r="Q185" s="10" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
-      <c r="R185" s="11" t="inlineStr">
-        <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="B186" s="8" t="inlineStr">
-        <is>
-          <t>未发生替换仍未命中Hand</t>
-        </is>
-      </c>
-      <c r="C186" s="8" t="inlineStr">
-        <is>
-          <t>Hand生产库未命中</t>
-        </is>
-      </c>
-      <c r="D186" s="8" t="inlineStr">
-        <is>
-          <t>XJ-B-202311001</t>
-        </is>
-      </c>
-      <c r="E186" s="9" t="inlineStr">
-        <is>
-          <t>《香蕉》徐培博独家经济合同</t>
-        </is>
-      </c>
-      <c r="F186" s="8" t="inlineStr">
-        <is>
-          <t>2028-06-20</t>
-        </is>
-      </c>
-      <c r="G186" s="8" t="inlineStr">
-        <is>
-          <t>法务确认</t>
-        </is>
-      </c>
-      <c r="H186" s="8" t="inlineStr">
-        <is>
-          <t>27115</t>
-        </is>
-      </c>
-      <c r="I186" s="8" t="inlineStr">
-        <is>
-          <t>27115</t>
-        </is>
-      </c>
-      <c r="J186" s="8" t="inlineStr"/>
-      <c r="K186" s="9" t="inlineStr"/>
-      <c r="L186" s="8" t="inlineStr">
-        <is>
-          <t>吴均远</t>
-        </is>
-      </c>
-      <c r="M186" s="8" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
-      <c r="N186" s="8" t="inlineStr">
-        <is>
-          <t>徐如珺1</t>
-        </is>
-      </c>
-      <c r="O186" s="8" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
-      <c r="P186" s="8" t="inlineStr">
-        <is>
-          <t>李家琪</t>
-        </is>
-      </c>
-      <c r="Q186" s="8" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
-      <c r="R186" s="9" t="inlineStr">
-        <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="B187" s="10" t="inlineStr">
-        <is>
-          <t>未发生替换仍未命中Hand</t>
-        </is>
-      </c>
-      <c r="C187" s="10" t="inlineStr">
-        <is>
-          <t>Hand生产库未命中</t>
-        </is>
-      </c>
-      <c r="D187" s="10" t="inlineStr">
-        <is>
-          <t>XJ-B-202401001</t>
-        </is>
-      </c>
-      <c r="E187" s="11" t="inlineStr">
-        <is>
-          <t>重越_独家经纪合同（通用版）_20230221_V2.3</t>
-        </is>
-      </c>
-      <c r="F187" s="10" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="G187" s="10" t="inlineStr">
-        <is>
-          <t>归档</t>
-        </is>
-      </c>
-      <c r="H187" s="10" t="inlineStr">
-        <is>
-          <t>14975</t>
-        </is>
-      </c>
-      <c r="I187" s="10" t="inlineStr">
-        <is>
-          <t>14975</t>
-        </is>
-      </c>
-      <c r="J187" s="10" t="inlineStr"/>
-      <c r="K187" s="11" t="inlineStr"/>
-      <c r="L187" s="10" t="inlineStr">
-        <is>
-          <t>宋頔斐</t>
-        </is>
-      </c>
-      <c r="M187" s="10" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
-      <c r="N187" s="10" t="inlineStr">
-        <is>
-          <t>宋頔斐</t>
-        </is>
-      </c>
-      <c r="O187" s="10" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
-      <c r="P187" s="10" t="inlineStr">
-        <is>
-          <t>李家琪</t>
-        </is>
-      </c>
-      <c r="Q187" s="10" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
-      <c r="R187" s="11" t="inlineStr">
-        <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="B188" s="8" t="inlineStr">
-        <is>
-          <t>未发生替换仍未命中Hand</t>
-        </is>
-      </c>
-      <c r="C188" s="8" t="inlineStr">
-        <is>
-          <t>Hand生产库未命中</t>
-        </is>
-      </c>
-      <c r="D188" s="8" t="inlineStr">
-        <is>
-          <t>XJ-B-202402001</t>
-        </is>
-      </c>
-      <c r="E188" s="9" t="inlineStr">
-        <is>
-          <t>王梓源_独家经纪合同（通用版）_20230221_V2.3</t>
-        </is>
-      </c>
-      <c r="F188" s="8" t="inlineStr">
-        <is>
-          <t>2029-02-28</t>
-        </is>
-      </c>
-      <c r="G188" s="8" t="inlineStr">
-        <is>
-          <t>归档</t>
-        </is>
-      </c>
-      <c r="H188" s="8" t="inlineStr">
-        <is>
-          <t>28224</t>
-        </is>
-      </c>
-      <c r="I188" s="8" t="inlineStr">
-        <is>
-          <t>28224</t>
-        </is>
-      </c>
-      <c r="J188" s="8" t="inlineStr"/>
-      <c r="K188" s="9" t="inlineStr"/>
-      <c r="L188" s="8" t="inlineStr">
-        <is>
-          <t>宋頔斐1</t>
-        </is>
-      </c>
-      <c r="M188" s="8" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
-      <c r="N188" s="8" t="inlineStr">
-        <is>
-          <t>宋頔斐1</t>
-        </is>
-      </c>
-      <c r="O188" s="8" t="inlineStr">
-        <is>
-          <t>离职</t>
-        </is>
-      </c>
-      <c r="P188" s="8" t="inlineStr">
-        <is>
-          <t>李家琪</t>
-        </is>
-      </c>
-      <c r="Q188" s="8" t="inlineStr">
-        <is>
-          <t>在职</t>
-        </is>
-      </c>
-      <c r="R188" s="9" t="inlineStr">
-        <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:R188"/>
+  <autoFilter ref="A1:R184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/contract_anchor_db/Hand主播档案仍未命中_替换后_20260629.xlsx
+++ b/output/contract_anchor_db/Hand主播档案仍未命中_替换后_20260629.xlsx
@@ -3460,7 +3460,7 @@
       </c>
       <c r="P34" s="8" t="inlineStr">
         <is>
-          <t>汤澄</t>
+          <t>李家琪</t>
         </is>
       </c>
       <c r="Q34" s="8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="R34" s="9" t="inlineStr">
         <is>
-          <t>申请人离职,合同执行人离职/缺失,更新为李家琪; 法务CSV合同流程接收人最终覆盖为汤澄</t>
+          <t>申请人离职,合同执行人离职/缺失,更新为李家琪</t>
         </is>
       </c>
     </row>
